--- a/docs/xlsx/jobs-2026-09-08.xlsx
+++ b/docs/xlsx/jobs-2026-09-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="386">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1147 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Community Assistance Fellow – AmeriCorps</t>
+  </si>
+  <si>
+    <t>Conservation Legacy Program: Stewards Individual Placements Program</t>
+  </si>
+  <si>
+    <t>Westlake Village, CA</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$600 per week</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-assistance-fellow--americorps-1-baxter-way-suite-180-westlake-village-ca-91362-california/3591200421</t>
+  </si>
+  <si>
+    <t>Fire and Stewardship Manager</t>
+  </si>
+  <si>
+    <t>LAD Foundation/Pioneer Forest</t>
+  </si>
+  <si>
+    <t>Salem, MO</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$60,804 - $85,125 per year</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fire-and-stewardship-manager-salem-missouri/1072777623</t>
+  </si>
+  <si>
+    <t>Green Corps Campaigner</t>
+  </si>
+  <si>
+    <t>Green Corps</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>Pay and benefits are prorated for the length of your campaign position. The target annual compensation for this position is $40,000 (but compensation may range between $40,000 and $44,450 depending on location and start date).</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-green-corps-campaigner-portland-oregon/9386124420</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-green-corps-campaigner-oakland-california/8259077401</t>
+  </si>
+  <si>
+    <t>Resource Technician</t>
+  </si>
+  <si>
+    <t>Kane DuPage Soil &amp; Water Conservation District</t>
+  </si>
+  <si>
+    <t>St Charles, IL</t>
+  </si>
+  <si>
+    <t>$52,000 - $62,400 per year</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-resource-technician-st-charles-illinois/2940783169</t>
+  </si>
+  <si>
+    <t>USDA-ARS Research Fellowship in Conservation and Water-Efficient Cropping Systems</t>
+  </si>
+  <si>
+    <t>U.S. Department of Agriculture (USDA)</t>
+  </si>
+  <si>
+    <t>Parlier, CA</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>Stipend $75,055.00 – $92,958.00 Yearly</t>
+  </si>
+  <si>
+    <t>botany-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-research-fellowship-in-conservation-and-water-efficient-cropping-systems-parlier-california/7119628999</t>
+  </si>
+  <si>
+    <t>¡Buscamos Analista de Alianzas y Estrategias para Fundraising!</t>
+  </si>
+  <si>
+    <t>Por el Mar</t>
+  </si>
+  <si>
+    <t>San Isidro, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 1800.00 - 1800.00/month</t>
+  </si>
+  <si>
+    <t>Environment, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6249156aba82498eb3e0b28c3cf2d91b-buscamos-analista-de-alianzas-y-estrategias-para-fundraising-por-el-mar-san-isidro</t>
+  </si>
+  <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Congregation Mishkan Israel</t>
+  </si>
+  <si>
+    <t>Hamden, Connecticut</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Race Ethnicity, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af502b39f43248c7b556d350c62ace65-administrative-assistant-congregation-mishkan-israel-hamden</t>
+  </si>
+  <si>
+    <t>After School Content Specialist Middle School</t>
+  </si>
+  <si>
+    <t>Zone 126</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf15e120d9fe48399dba0701c3d3cf13-after-school-content-specialist-middle-school-zone-126-queens-county</t>
+  </si>
+  <si>
+    <t>Application Reviewer, Community Schools Rental Assistance Program (CSRAP)</t>
+  </si>
+  <si>
+    <t>Housing Initiative Partnership, Inc.</t>
+  </si>
+  <si>
+    <t>Hyattsville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Financial Literacy Personal Finance, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/085afc6d2a1c4a63a87592222d160bd8-application-reviewer-community-schools-rental-assistance-program-csrap-housing-initiative-partnership-inc-hyattsville</t>
+  </si>
+  <si>
+    <t>Asistente de Comunicación (Prensa y Redacción)</t>
+  </si>
+  <si>
+    <t>Haciendo Camino Asoc. Civil</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65bbb009f37d4773ae754faab94c4d24-asistente-de-comunicacion-prensa-y-redaccion-haciendo-camino-asoc-civil-buenos-aires</t>
+  </si>
+  <si>
+    <t>ASL Fluent Community-Based Direct Support Professional (DSP)</t>
+  </si>
+  <si>
+    <t>Toolworks</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd7a2b0c159e4970b3c606938c0f0d0b-asl-fluent-community-based-direct-support-professional-dsp-toolworks-san-francisco</t>
+  </si>
+  <si>
+    <t>Assistant Director (P/T Variable) Department Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>AJC</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 34.00 - 36.00/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Religion Spirituality, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c21b40e11d9046b28d0ec03e382179f0-assistant-director-pt-variable-department-philadelphia-pa-ajc-philadelphia</t>
+  </si>
+  <si>
+    <t>Assistant Field Manager, Environmental (Job #371) ($101,299 - $111,778)</t>
+  </si>
+  <si>
+    <t>Rural Community Assistance Corporation (RCAC)</t>
+  </si>
+  <si>
+    <t>Anchorage, Alaska</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fabc9fdb494a4145b8f2123609ed31d2-assistant-field-manager-environmental-job-371-101299-111778-rural-community-assistance-corporation-rcac-anchorage</t>
+  </si>
+  <si>
+    <t>Associate Director of Talent Operations</t>
+  </si>
+  <si>
+    <t>Reproductive Freedom for All</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Policy, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/59d83a0e1f304d209726d170d7207c7c-associate-director-of-talent-operations-reproductive-freedom-for-all-washington</t>
+  </si>
+  <si>
+    <t>Associate Vice President of Workforce Strategies</t>
+  </si>
+  <si>
+    <t>American Association of Community Colleges</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1c50ec247e346e7bc125105b4c95c18-associate-vice-president-of-workforce-strategies-american-association-of-community-colleges-washington</t>
+  </si>
+  <si>
+    <t>AVP, Data &amp; Intelligence</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/348ec41675644624af2196987590cd4c-avp-data-intelligence-american-association-of-community-colleges-washington</t>
+  </si>
+  <si>
+    <t>AVP, Learning Ecosystems and Student Affairs</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d1d9950ac0374e54afb2e45b8eed90b7-avp-learning-ecosystems-and-student-affairs-american-association-of-community-colleges-washington</t>
+  </si>
+  <si>
+    <t>Bilingual Administrative Assistant in Los Angeles</t>
+  </si>
+  <si>
+    <t>Immigration Center for Women and Children</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Immigrants Or Refugees, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/618d8ab560794b23809f87b494c5dc0d-bilingual-administrative-assistant-in-los-angeles-immigration-center-for-women-and-children-los-angeles</t>
+  </si>
+  <si>
+    <t>Budget &amp; Fiscal Analyst</t>
+  </si>
+  <si>
+    <t>Fines and Fees Justice Center</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 92500.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8fe3e90dd4004087b85ff668047319dc-budget-fiscal-analyst-fines-and-fees-justice-center-new-york</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>FOUNDERS FIRST COMMUNITY DEVELOPMENT CORPORATION INC</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Lgbtq, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fdddd9b2c11244849fb991f23c7092b5-chief-executive-officer-founders-first-community-development-corporation-inc-san-diego</t>
+  </si>
+  <si>
+    <t>Chief Impact Officer</t>
+  </si>
+  <si>
+    <t>Pure Earth/Blacksmith Institute</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 200000.00 - 230000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Environment, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c450799d2fe040eaab05d5f2d328fe6d-chief-impact-officer-pure-earthblacksmith-institute-new-york</t>
+  </si>
+  <si>
+    <t>Clinical Operations Lead</t>
+  </si>
+  <si>
+    <t>1Day Sooner</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/019edf0622fe442fabb9bb6289e6d1eb-clinical-operations-lead-1day-sooner-brooklyn</t>
+  </si>
+  <si>
+    <t>Communications Assistant</t>
+  </si>
+  <si>
+    <t>Library Foundation of Los Angeles</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 27.50/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/728af1ef388d4ac3b288b43f17b0bd2f-communications-assistant-library-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Communications Manager (Contractor)</t>
+  </si>
+  <si>
+    <t>Elba Hope Foundation</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Children Youth, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9bd60116792944758240ff392908e87a-communications-manager-contractor-elba-hope-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Community Food Program Associate</t>
+  </si>
+  <si>
+    <t>A Place To Turn</t>
+  </si>
+  <si>
+    <t>Natick, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d79914a2de5c408393ac8a3e9f0eb39d-community-food-program-associate-a-place-to-turn-natick</t>
+  </si>
+  <si>
+    <t>Data and Evaluation Coordinator</t>
+  </si>
+  <si>
+    <t>Neighborhood House</t>
+  </si>
+  <si>
+    <t>Saint Paul, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5711bee97bdb40f29eb69dc7dfb99dff-data-and-evaluation-coordinator-neighborhood-house-saint-paul</t>
+  </si>
+  <si>
+    <t>Data Center Associate</t>
+  </si>
+  <si>
+    <t>Minnesota Center for Environmental Advocacy</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 31.25 - 33.65/hour</t>
+  </si>
+  <si>
+    <t>Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c5a21c27390485f8e512de54faefc3f-data-center-associate-minnesota-center-for-environmental-advocacy-saint-paul</t>
+  </si>
+  <si>
+    <t>Development Coordinator Donor Relations</t>
+  </si>
+  <si>
+    <t>Seva Foundation</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 33.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3a8c0e354c44664a3191d5a2746c99d-development-coordinator-donor-relations-seva-foundation-berkeley</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Ironbound Community Corporation of Newark, NJ</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4bd1e3668c9140028bfe81d42b2e3a8d-development-director-ironbound-community-corporation-of-newark-nj-newark</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>UNCF</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 71000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e55137905ca4ac6bdc996cd81ed995b-development-manager-uncf-washington</t>
+  </si>
+  <si>
+    <t>Director of Asset Management</t>
+  </si>
+  <si>
+    <t>HRI (Homeowner's Rehab, Inc.)</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f8eb3c4124a4e499768439595e2572d-director-of-asset-management-hri-homeowners-rehab-inc-cambridge</t>
+  </si>
+  <si>
+    <t>Director of Clinical Trials</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8ffd2a19a39643cfb403b048ee698eea-director-of-clinical-trials-1day-sooner-brooklyn</t>
+  </si>
+  <si>
+    <t>Director of Community Organizing and Coalitions</t>
+  </si>
+  <si>
+    <t>Issue One</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c8a99d31fb534bfab2d128396399432e-director-of-community-organizing-and-coalitions-issue-one-washington</t>
+  </si>
+  <si>
+    <t>Director of Development and Communications</t>
+  </si>
+  <si>
+    <t>Custom Collaborative</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/687f2a5b8a0941afa31eb20f737f80f7-director-of-development-and-communications-custom-collaborative-new-york</t>
+  </si>
+  <si>
+    <t>Director of HR &amp; Culture</t>
+  </si>
+  <si>
+    <t>Southern Service Workers Education Fund, Inc.</t>
+  </si>
+  <si>
+    <t>Durham, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2716a12f5d9b47559a3e37ce699df733-director-of-hr-culture-southern-service-workers-education-fund-inc-durham</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>The HR Source</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27139b31621e4091a165c7682a64a27c-director-of-operations-the-hr-source-prince-georges-county</t>
+  </si>
+  <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bb5ba070867845998e1b57e7f77f5688-director-of-programs-the-hr-source-prince-georges-county</t>
+  </si>
+  <si>
+    <t>Director of Real Estate and Asset Management</t>
+  </si>
+  <si>
+    <t>Greater Jamaica Development Corporation</t>
+  </si>
+  <si>
+    <t>Jamaica, NY</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2991299f468e471e8bac0e523a19a8fd-director-of-real-estate-and-asset-management-greater-jamaica-development-corporation-jamaica</t>
+  </si>
+  <si>
+    <t>Director, Foundations &amp; Grants</t>
+  </si>
+  <si>
+    <t>Partnership for a Healthier America</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/154cbf8781e549a283043803d3403aa1-director-foundations-grants-partnership-for-a-healthier-america-washington</t>
+  </si>
+  <si>
+    <t>Director, Institutional Giving</t>
+  </si>
+  <si>
+    <t>Repair the World</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bce64aa388e94e05ac87a9ce56cbe4c6-director-institutional-giving-repair-the-world-new-york</t>
+  </si>
+  <si>
+    <t>Education Coordinator</t>
+  </si>
+  <si>
+    <t>Neponset River Watershed Association</t>
+  </si>
+  <si>
+    <t>Canton, MA</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5361f81e4d6421293ec4e5464eea594-education-coordinator-neponset-river-watershed-association-canton</t>
+  </si>
+  <si>
+    <t>Employment Attorney/Of Counsel</t>
+  </si>
+  <si>
+    <t>Harmon Curran Spielberg &amp; Eisenberg, LLP</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/5846e473ec4b49f9b92878e776624182-employment-attorneyof-counsel-harmon-curran-spielberg-eisenberg-llp-washington</t>
+  </si>
+  <si>
+    <t>Entry-Level to Experienced Teacher</t>
+  </si>
+  <si>
+    <t>Success Academy Charter Schools</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13846e3aa90749b08d1e0f55ff9da966-entry-level-to-experienced-teacher-success-academy-charter-schools-new-york</t>
+  </si>
+  <si>
+    <t>Environmental Educator</t>
+  </si>
+  <si>
+    <t>Ecology Center, Ann Arbor</t>
+  </si>
+  <si>
+    <t>Ann Arbor, Michigan</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ccf5e92af4f64c2297bd892cb6164891-environmental-educator-ecology-center-ann-arbor-ann-arbor</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Lopez Community Land Trust</t>
+  </si>
+  <si>
+    <t>Lopez Island, Washington</t>
+  </si>
+  <si>
+    <t>USD 117000.00 - 134000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e4f2f23fc66d476980b895cbd1fa5c95-executive-director-lopez-community-land-trust-lopez-island</t>
+  </si>
+  <si>
+    <t>Foodnet Meals on Wheels</t>
+  </si>
+  <si>
+    <t>Ithaca, New York</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Community Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72e2456b728848b09ab0bcdd3e9e3b12-executive-director-foodnet-meals-on-wheels-ithaca</t>
+  </si>
+  <si>
+    <t>West Virginians for Affordable Health Care</t>
+  </si>
+  <si>
+    <t>Charleston, West Virginia</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Policy, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca00e76b20b2432697c473793ac9456a-executive-director-west-virginians-for-affordable-health-care-charleston</t>
+  </si>
+  <si>
+    <t>EXECUTIVE DIRECTOR FOR A RARE DISEASE FOUNDATION</t>
+  </si>
+  <si>
+    <t>The DDX3X Foundation</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/07afc3405da44a9f8e431093d3049a07-executive-director-for-a-rare-disease-foundation-the-ddx3x-foundation-wilmington</t>
+  </si>
+  <si>
+    <t>Facilities Director</t>
+  </si>
+  <si>
+    <t>Kaufman Music Center</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05662c6a13254fc99b349d5d8f5ace1f-facilities-director-kaufman-music-center-new-york</t>
+  </si>
+  <si>
+    <t>Fractional Development Director</t>
+  </si>
+  <si>
+    <t>Period Education Project</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 75.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b70f92591a64fa880940927daeb9a23-fractional-development-director-period-education-project-greenville</t>
+  </si>
+  <si>
+    <t>Grounds and Buildings Manager</t>
+  </si>
+  <si>
+    <t>North10 Philadelphia</t>
+  </si>
+  <si>
+    <t>USD 55000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Urban Areas, Water Sanitation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c74822e4c5ab41909977ed922dfc0a67-grounds-and-buildings-manager-north10-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Housing &amp; Financial Counselor</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a3b090cb0417405594916137e09d7953-housing-financial-counselor-housing-initiative-partnership-inc-hyattsville</t>
+  </si>
+  <si>
+    <t>Legal Fellow (Full-time)</t>
+  </si>
+  <si>
+    <t>Fair Housing Advocates of Northern California</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7948c28cc02a4bf18a08e5c4ba3d2c0f-legal-fellow-full-time-fair-housing-advocates-of-northern-california-san-rafael</t>
+  </si>
+  <si>
+    <t>Licensed Mental Health Counselor</t>
+  </si>
+  <si>
+    <t>Center for Independence of the Disabled, NY</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a7630d61d184403a65c8c6a178b8ae2-licensed-mental-health-counselor-center-for-independence-of-the-disabled-ny-new-york</t>
+  </si>
+  <si>
+    <t>MA/ RI Community Organizer (candidates can be based anywhere in Eastern MA)</t>
+  </si>
+  <si>
+    <t>Slingshot -</t>
+  </si>
+  <si>
+    <t>Remote (Worcester, Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/864f594923ad4247b5f6d60a6ace84f9-ma-ri-community-organizer-candidates-can-be-based-anywhere-in-eastern-ma-slingshot-worcester</t>
+  </si>
+  <si>
+    <t>Remote (Boston, Massachusetts)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6bac742af5f5431798b6144cae68ad52-ma-ri-community-organizer-candidates-can-be-based-anywhere-in-eastern-ma-slingshot-boston</t>
+  </si>
+  <si>
+    <t>Major Gift Officer</t>
+  </si>
+  <si>
+    <t>All Our Kin</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9866c8d76772470c9ef6e51eda951d33-major-gift-officer-all-our-kin-new-haven</t>
+  </si>
+  <si>
+    <t>Manager of Payroll &amp; HRIS Operations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63033d1b9e43460d85103045a8036976-manager-of-payroll-hris-operations-greater-jamaica-development-corporation-queens-county</t>
+  </si>
+  <si>
+    <t>Manager, Direct Marketing</t>
+  </si>
+  <si>
+    <t>NAACP Legal Defense and Educational Fund, Inc.</t>
+  </si>
+  <si>
+    <t>USD 74400.00 - 103000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a98e96885a7740d6b63e11b85795103f-manager-direct-marketing-naacp-legal-defense-and-educational-fund-inc-washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13d83e657e6743e98ffb57e5de8980e8-manager-direct-marketing-naacp-legal-defense-and-educational-fund-inc-new-york</t>
+  </si>
+  <si>
+    <t>Membership Coordinator</t>
+  </si>
+  <si>
+    <t>National Volunteer Fire Council</t>
+  </si>
+  <si>
+    <t>USD 56668.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e94c477f2144ba39d34211d0ed11d07-membership-coordinator-national-volunteer-fire-council-washington</t>
+  </si>
+  <si>
+    <t>Monitoring, Evaluation, Accountability &amp; Learning (MEAL) Advisor (Contract)</t>
+  </si>
+  <si>
+    <t>USD 28000.00 - 28000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/002cc99c47ab4f0e97a83b6a252976bf-monitoring-evaluation-accountability-learning-meal-advisor-contract-elba-hope-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Office Administrator &amp; Executive Assistant (Full-time)</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 66000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b826f1d2212d4bdf8ae5b04651a74910-office-administrator-executive-assistant-full-time-fair-housing-advocates-of-northern-california-san-rafael</t>
+  </si>
+  <si>
+    <t>Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Documented</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bae80ee396364e4ca03956f2174630d3-operations-coordinator-documented-new-york</t>
+  </si>
+  <si>
+    <t>Paralegal Case Manager</t>
+  </si>
+  <si>
+    <t>Housing Rights Center</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7efe673c3c544eaca7e6537efb919279-paralegal-case-manager-housing-rights-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Part Time Teaching Artist, Music</t>
+  </si>
+  <si>
+    <t>A Place Called Home</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbbcba51a9f64897bc69ff7ca2fe161d-part-time-teaching-artist-music-a-place-called-home-los-angeles</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 42.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5f5c92d105e4c74acc6fc5cf16f1e2c-project-manager-the-hr-source-arlington</t>
+  </si>
+  <si>
+    <t>Senior Director of Digital Communications</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 205000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da8bc786fea543eb85120f3e7644a043-senior-director-of-digital-communications-reproductive-freedom-for-all-washington</t>
+  </si>
+  <si>
+    <t>Social Media Campaign Strategist/Senior Strategist</t>
+  </si>
+  <si>
+    <t>Human Rights First</t>
+  </si>
+  <si>
+    <t>USD 69870.00 - 80232.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10ad03c49a214835b0cc81cee32b4f49-social-media-campaign-strategistsenior-strategist-human-rights-first-new-york</t>
+  </si>
+  <si>
+    <t>Specialist, Assessment</t>
+  </si>
+  <si>
+    <t>Chef Ann Foundation</t>
+  </si>
+  <si>
+    <t>Boulder, CO</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/aabd17f60e28463da56b2edd08713e7d-specialist-assessment-chef-ann-foundation-boulder</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b47dd6b025f24974ab35b8f8909e59fa-staff-accountant-housing-initiative-partnership-inc-hyattsville</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 82000.00 - 86000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e2725a1aedc4318a5b686f5342eda31-staff-attorney-fair-housing-advocates-of-northern-california-san-rafael</t>
+  </si>
+  <si>
+    <t>Staff Attorney I or II</t>
+  </si>
+  <si>
+    <t>Garment Worker Center</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 103740.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d00e27039fba414b84c5a3dfb37f7395-staff-attorney-i-or-ii-garment-worker-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Temporary Rental Assistance Program Coordinator</t>
+  </si>
+  <si>
+    <t>USD 53000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0dab0c22d8af420aaa5d8c37d5d2cce6-temporary-rental-assistance-program-coordinator-housing-rights-center-los-angeles</t>
+  </si>
+  <si>
+    <t>User Support Technician I</t>
+  </si>
+  <si>
+    <t>Central Park Conservancy</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd81b8fd75f14c0fa6fc114d23062256-user-support-technician-i-central-park-conservancy-new-york</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1188,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1214,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +1557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +1596,154 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +1799,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +1838,1690 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" t="s">
+        <v>129</v>
+      </c>
+      <c r="F17" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" t="s">
+        <v>135</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19" t="s">
+        <v>140</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>142</v>
+      </c>
+      <c r="B20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F20" t="s">
+        <v>145</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" t="s">
+        <v>151</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" t="s">
+        <v>155</v>
+      </c>
+      <c r="D22" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" t="s">
+        <v>156</v>
+      </c>
+      <c r="F22" t="s">
+        <v>157</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C23" t="s">
+        <v>155</v>
+      </c>
+      <c r="D23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" t="s">
+        <v>162</v>
+      </c>
+      <c r="F23" t="s">
+        <v>163</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" t="s">
+        <v>135</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" t="s">
+        <v>172</v>
+      </c>
+      <c r="D25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" t="s">
+        <v>178</v>
+      </c>
+      <c r="F26" t="s">
+        <v>104</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" t="s">
+        <v>183</v>
+      </c>
+      <c r="F27" t="s">
+        <v>184</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>186</v>
+      </c>
+      <c r="B28" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" t="s">
+        <v>187</v>
+      </c>
+      <c r="F28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>189</v>
+      </c>
+      <c r="B29" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" t="s">
+        <v>191</v>
+      </c>
+      <c r="F29" t="s">
+        <v>192</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>194</v>
+      </c>
+      <c r="B30" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" t="s">
+        <v>196</v>
+      </c>
+      <c r="F30" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>199</v>
+      </c>
+      <c r="B31" t="s">
+        <v>200</v>
+      </c>
+      <c r="C31" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31" t="s">
+        <v>54</v>
+      </c>
+      <c r="E31" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" t="s">
+        <v>203</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>205</v>
+      </c>
+      <c r="B32" t="s">
+        <v>206</v>
+      </c>
+      <c r="C32" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" t="s">
+        <v>207</v>
+      </c>
+      <c r="F32" t="s">
+        <v>208</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>210</v>
+      </c>
+      <c r="B33" t="s">
+        <v>206</v>
+      </c>
+      <c r="C33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" t="s">
+        <v>211</v>
+      </c>
+      <c r="F33" t="s">
+        <v>212</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>214</v>
+      </c>
+      <c r="B34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" t="s">
+        <v>216</v>
+      </c>
+      <c r="D34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" t="s">
+        <v>217</v>
+      </c>
+      <c r="F34" t="s">
+        <v>218</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>220</v>
+      </c>
+      <c r="B35" t="s">
+        <v>221</v>
+      </c>
+      <c r="C35" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" t="s">
+        <v>222</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>224</v>
+      </c>
+      <c r="B36" t="s">
+        <v>225</v>
+      </c>
+      <c r="C36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" t="s">
+        <v>226</v>
+      </c>
+      <c r="F36" t="s">
+        <v>227</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" t="s">
+        <v>231</v>
+      </c>
+      <c r="D37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" t="s">
+        <v>232</v>
+      </c>
+      <c r="F37" t="s">
+        <v>233</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>235</v>
+      </c>
+      <c r="B38" t="s">
+        <v>236</v>
+      </c>
+      <c r="C38" t="s">
+        <v>237</v>
+      </c>
+      <c r="D38" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" t="s">
+        <v>238</v>
+      </c>
+      <c r="F38" t="s">
+        <v>239</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>241</v>
+      </c>
+      <c r="B39" t="s">
+        <v>242</v>
+      </c>
+      <c r="C39" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" t="s">
+        <v>243</v>
+      </c>
+      <c r="F39" t="s">
+        <v>244</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>246</v>
+      </c>
+      <c r="B40" t="s">
+        <v>247</v>
+      </c>
+      <c r="C40" t="s">
+        <v>248</v>
+      </c>
+      <c r="D40" t="s">
+        <v>249</v>
+      </c>
+      <c r="E40" t="s">
+        <v>250</v>
+      </c>
+      <c r="F40" t="s">
+        <v>251</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>253</v>
+      </c>
+      <c r="B41" t="s">
+        <v>254</v>
+      </c>
+      <c r="C41" t="s">
+        <v>255</v>
+      </c>
+      <c r="D41" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" t="s">
+        <v>256</v>
+      </c>
+      <c r="F41" t="s">
+        <v>257</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>253</v>
+      </c>
+      <c r="B42" t="s">
+        <v>259</v>
+      </c>
+      <c r="C42" t="s">
+        <v>260</v>
+      </c>
+      <c r="D42" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" t="s">
+        <v>261</v>
+      </c>
+      <c r="F42" t="s">
+        <v>262</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>253</v>
+      </c>
+      <c r="B43" t="s">
+        <v>264</v>
+      </c>
+      <c r="C43" t="s">
+        <v>265</v>
+      </c>
+      <c r="D43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" t="s">
+        <v>266</v>
+      </c>
+      <c r="F43" t="s">
+        <v>267</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>269</v>
+      </c>
+      <c r="B44" t="s">
+        <v>270</v>
+      </c>
+      <c r="C44" t="s">
+        <v>116</v>
+      </c>
+      <c r="D44" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" t="s">
+        <v>271</v>
+      </c>
+      <c r="F44" t="s">
+        <v>272</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>274</v>
+      </c>
+      <c r="B45" t="s">
+        <v>275</v>
+      </c>
+      <c r="C45" t="s">
+        <v>128</v>
+      </c>
+      <c r="D45" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" t="s">
+        <v>276</v>
+      </c>
+      <c r="F45" t="s">
+        <v>277</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>279</v>
+      </c>
+      <c r="B46" t="s">
+        <v>280</v>
+      </c>
+      <c r="C46" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" t="s">
+        <v>281</v>
+      </c>
+      <c r="F46" t="s">
+        <v>282</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>284</v>
+      </c>
+      <c r="B47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C47" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" t="s">
+        <v>286</v>
+      </c>
+      <c r="F47" t="s">
+        <v>287</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>289</v>
+      </c>
+      <c r="B48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" t="s">
+        <v>54</v>
+      </c>
+      <c r="E48" t="s">
+        <v>290</v>
+      </c>
+      <c r="F48" t="s">
+        <v>69</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>292</v>
+      </c>
+      <c r="B49" t="s">
+        <v>293</v>
+      </c>
+      <c r="C49" t="s">
+        <v>294</v>
+      </c>
+      <c r="D49" t="s">
+        <v>249</v>
+      </c>
+      <c r="E49" t="s">
+        <v>295</v>
+      </c>
+      <c r="F49" t="s">
+        <v>296</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>298</v>
+      </c>
+      <c r="B50" t="s">
+        <v>299</v>
+      </c>
+      <c r="C50" t="s">
+        <v>128</v>
+      </c>
+      <c r="D50" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" t="s">
+        <v>300</v>
+      </c>
+      <c r="F50" t="s">
+        <v>301</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>303</v>
+      </c>
+      <c r="B51" t="s">
+        <v>304</v>
+      </c>
+      <c r="C51" t="s">
+        <v>305</v>
+      </c>
+      <c r="D51" t="s">
+        <v>54</v>
+      </c>
+      <c r="E51" t="s">
+        <v>306</v>
+      </c>
+      <c r="F51" t="s">
+        <v>307</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>303</v>
+      </c>
+      <c r="B52" t="s">
+        <v>304</v>
+      </c>
+      <c r="C52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D52" t="s">
+        <v>54</v>
+      </c>
+      <c r="E52" t="s">
+        <v>306</v>
+      </c>
+      <c r="F52" t="s">
+        <v>307</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>311</v>
+      </c>
+      <c r="B53" t="s">
+        <v>312</v>
+      </c>
+      <c r="C53" t="s">
+        <v>122</v>
+      </c>
+      <c r="D53" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" t="s">
+        <v>313</v>
+      </c>
+      <c r="F53" t="s">
+        <v>314</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>316</v>
+      </c>
+      <c r="B54" t="s">
+        <v>215</v>
+      </c>
+      <c r="C54" t="s">
+        <v>60</v>
+      </c>
+      <c r="D54" t="s">
+        <v>54</v>
+      </c>
+      <c r="E54" t="s">
+        <v>261</v>
+      </c>
+      <c r="F54" t="s">
+        <v>218</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>318</v>
+      </c>
+      <c r="B55" t="s">
+        <v>319</v>
+      </c>
+      <c r="C55" t="s">
+        <v>94</v>
+      </c>
+      <c r="D55" t="s">
+        <v>54</v>
+      </c>
+      <c r="E55" t="s">
+        <v>320</v>
+      </c>
+      <c r="F55" t="s">
+        <v>321</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>318</v>
+      </c>
+      <c r="B56" t="s">
+        <v>319</v>
+      </c>
+      <c r="C56" t="s">
+        <v>128</v>
+      </c>
+      <c r="D56" t="s">
+        <v>54</v>
+      </c>
+      <c r="E56" t="s">
+        <v>320</v>
+      </c>
+      <c r="F56" t="s">
+        <v>321</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>324</v>
+      </c>
+      <c r="B57" t="s">
+        <v>325</v>
+      </c>
+      <c r="C57" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57" t="s">
+        <v>54</v>
+      </c>
+      <c r="E57" t="s">
+        <v>326</v>
+      </c>
+      <c r="F57" t="s">
+        <v>74</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>328</v>
+      </c>
+      <c r="B58" t="s">
+        <v>143</v>
+      </c>
+      <c r="C58" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58" t="s">
+        <v>47</v>
+      </c>
+      <c r="E58" t="s">
+        <v>329</v>
+      </c>
+      <c r="F58" t="s">
+        <v>145</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>331</v>
+      </c>
+      <c r="B59" t="s">
+        <v>293</v>
+      </c>
+      <c r="C59" t="s">
+        <v>294</v>
+      </c>
+      <c r="D59" t="s">
+        <v>54</v>
+      </c>
+      <c r="E59" t="s">
+        <v>332</v>
+      </c>
+      <c r="F59" t="s">
+        <v>296</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>334</v>
+      </c>
+      <c r="B60" t="s">
+        <v>335</v>
+      </c>
+      <c r="C60" t="s">
+        <v>128</v>
+      </c>
+      <c r="D60" t="s">
+        <v>161</v>
+      </c>
+      <c r="E60" t="s">
+        <v>336</v>
+      </c>
+      <c r="F60" t="s">
+        <v>197</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>338</v>
+      </c>
+      <c r="B61" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" t="s">
+        <v>110</v>
+      </c>
+      <c r="D61" t="s">
+        <v>161</v>
+      </c>
+      <c r="E61" t="s">
+        <v>340</v>
+      </c>
+      <c r="F61" t="s">
+        <v>341</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>343</v>
+      </c>
+      <c r="B62" t="s">
+        <v>344</v>
+      </c>
+      <c r="C62" t="s">
+        <v>345</v>
+      </c>
+      <c r="D62" t="s">
+        <v>61</v>
+      </c>
+      <c r="E62" t="s">
+        <v>346</v>
+      </c>
+      <c r="F62" t="s">
+        <v>347</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>349</v>
+      </c>
+      <c r="B63" t="s">
+        <v>206</v>
+      </c>
+      <c r="C63" t="s">
+        <v>350</v>
+      </c>
+      <c r="D63" t="s">
+        <v>47</v>
+      </c>
+      <c r="E63" t="s">
+        <v>351</v>
+      </c>
+      <c r="F63" t="s">
+        <v>352</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>354</v>
+      </c>
+      <c r="B64" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" t="s">
+        <v>94</v>
+      </c>
+      <c r="D64" t="s">
+        <v>54</v>
+      </c>
+      <c r="E64" t="s">
+        <v>355</v>
+      </c>
+      <c r="F64" t="s">
+        <v>96</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>357</v>
+      </c>
+      <c r="B65" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" t="s">
+        <v>128</v>
+      </c>
+      <c r="D65" t="s">
+        <v>54</v>
+      </c>
+      <c r="E65" t="s">
+        <v>359</v>
+      </c>
+      <c r="F65" t="s">
+        <v>360</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>362</v>
+      </c>
+      <c r="B66" t="s">
+        <v>363</v>
+      </c>
+      <c r="C66" t="s">
+        <v>364</v>
+      </c>
+      <c r="D66" t="s">
+        <v>54</v>
+      </c>
+      <c r="E66" t="s">
+        <v>74</v>
+      </c>
+      <c r="F66" t="s">
+        <v>74</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>366</v>
+      </c>
+      <c r="B67" t="s">
+        <v>66</v>
+      </c>
+      <c r="C67" t="s">
+        <v>67</v>
+      </c>
+      <c r="D67" t="s">
+        <v>54</v>
+      </c>
+      <c r="E67" t="s">
+        <v>367</v>
+      </c>
+      <c r="F67" t="s">
+        <v>69</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>369</v>
+      </c>
+      <c r="B68" t="s">
+        <v>293</v>
+      </c>
+      <c r="C68" t="s">
+        <v>294</v>
+      </c>
+      <c r="D68" t="s">
+        <v>54</v>
+      </c>
+      <c r="E68" t="s">
+        <v>370</v>
+      </c>
+      <c r="F68" t="s">
+        <v>296</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>372</v>
+      </c>
+      <c r="B69" t="s">
+        <v>373</v>
+      </c>
+      <c r="C69" t="s">
+        <v>345</v>
+      </c>
+      <c r="D69" t="s">
+        <v>54</v>
+      </c>
+      <c r="E69" t="s">
+        <v>374</v>
+      </c>
+      <c r="F69" t="s">
+        <v>375</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>377</v>
+      </c>
+      <c r="B70" t="s">
+        <v>339</v>
+      </c>
+      <c r="C70" t="s">
+        <v>110</v>
+      </c>
+      <c r="D70" t="s">
+        <v>161</v>
+      </c>
+      <c r="E70" t="s">
+        <v>378</v>
+      </c>
+      <c r="F70" t="s">
+        <v>379</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>381</v>
+      </c>
+      <c r="B71" t="s">
+        <v>382</v>
+      </c>
+      <c r="C71" t="s">
+        <v>128</v>
+      </c>
+      <c r="D71" t="s">
+        <v>54</v>
+      </c>
+      <c r="E71" t="s">
+        <v>383</v>
+      </c>
+      <c r="F71" t="s">
+        <v>384</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-08.xlsx
+++ b/docs/xlsx/jobs-2026-09-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="852">
   <si>
     <t>Title</t>
   </si>
@@ -61,6 +61,27 @@
     <t>https://www.conservationjobboard.com/job-listing-community-assistance-fellow--americorps-1-baxter-way-suite-180-westlake-village-ca-91362-california/3591200421</t>
   </si>
   <si>
+    <t>Eastern Washington Fish Science Manager - WMS Band 2 - Permanent - 2026-07260</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Wenatchee, WA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$115,000 - $126,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-eastern-washington-fish-science-manager---wms-band-2---permanent---2026-07260-wenatchee-washington/5819052170</t>
+  </si>
+  <si>
     <t>Fire and Stewardship Manager</t>
   </si>
   <si>
@@ -70,9 +91,6 @@
     <t>Salem, MO</t>
   </si>
   <si>
-    <t>Permanent</t>
-  </si>
-  <si>
     <t>$60,804 - $85,125 per year</t>
   </si>
   <si>
@@ -169,6 +187,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/6249156aba82498eb3e0b28c3cf2d91b-buscamos-analista-de-alianzas-y-estrategias-para-fundraising-por-el-mar-san-isidro</t>
   </si>
   <si>
+    <t>Accounting Coordinator - Hybrid Sacramento CA</t>
+  </si>
+  <si>
+    <t>California Primary Care Association</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2d7b569791b4410bc0197893d31e277-accounting-coordinator-hybrid-sacramento-ca-california-primary-care-association-sacramento</t>
+  </si>
+  <si>
     <t>Administrative Assistant</t>
   </si>
   <si>
@@ -178,9 +214,6 @@
     <t>Hamden, Connecticut</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 20.00 - 28.00/hour</t>
   </si>
   <si>
@@ -190,6 +223,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/af502b39f43248c7b556d350c62ace65-administrative-assistant-congregation-mishkan-israel-hamden</t>
   </si>
   <si>
+    <t>Advocate (bilingual in English and Spanish)</t>
+  </si>
+  <si>
+    <t>The Network/La Red</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 59160.00 - 59160.00/year</t>
+  </si>
+  <si>
+    <t>Lgbtq, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72854da8332e4066be803f40c19e3213-advocate-bilingual-in-english-and-spanish-the-networkla-red-boston</t>
+  </si>
+  <si>
     <t>After School Content Specialist Middle School</t>
   </si>
   <si>
@@ -211,6 +262,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/cf15e120d9fe48399dba0701c3d3cf13-after-school-content-specialist-middle-school-zone-126-queens-county</t>
   </si>
   <si>
+    <t>Annual Fund Officer</t>
+  </si>
+  <si>
+    <t>Kakenya's Dream</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbab47fe028b4c56a4fa08f1a626981e-annual-fund-officer-kakenyas-dream-arlington</t>
+  </si>
+  <si>
     <t>Application Reviewer, Community Schools Rental Assistance Program (CSRAP)</t>
   </si>
   <si>
@@ -238,9 +307,6 @@
     <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Children Youth, Community Development, Health Medicine</t>
   </si>
   <si>
@@ -292,6 +358,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/fabc9fdb494a4145b8f2123609ed31d2-assistant-field-manager-environmental-job-371-101299-111778-rural-community-assistance-corporation-rcac-anchorage</t>
   </si>
   <si>
+    <t>Associate Director of Continuing Education - Hybrid Sacramento CA</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/403dddd97da04374aca2a1a86f67e0a6-associate-director-of-continuing-education-hybrid-sacramento-ca-california-primary-care-association-sacramento</t>
+  </si>
+  <si>
     <t>Associate Director of Talent Operations</t>
   </si>
   <si>
@@ -325,12 +397,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/e1c50ec247e346e7bc125105b4c95c18-associate-vice-president-of-workforce-strategies-american-association-of-community-colleges-washington</t>
   </si>
   <si>
+    <t>Associate Vice President, Data &amp; Intelligence</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/348ec41675644624af2196987590cd4c-associate-vice-president-data-intelligence-american-association-of-community-colleges-washington</t>
+  </si>
+  <si>
+    <t>Associate Vice President, Learning Ecosystems and Student Affairs</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d1d9950ac0374e54afb2e45b8eed90b7-associate-vice-president-learning-ecosystems-and-student-affairs-american-association-of-community-colleges-washington</t>
+  </si>
+  <si>
+    <t>Author Events &amp; Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>Justice Revival</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Religion Spirituality, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c46d67322af4c0cbee8d57b415bdb89-author-events-outreach-coordinator-justice-revival-washington</t>
+  </si>
+  <si>
     <t>AVP, Data &amp; Intelligence</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/348ec41675644624af2196987590cd4c-avp-data-intelligence-american-association-of-community-colleges-washington</t>
   </si>
   <si>
@@ -364,9 +466,6 @@
     <t>Fines and Fees Justice Center</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 85000.00 - 92500.00/year</t>
   </si>
   <si>
@@ -376,6 +475,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/8fe3e90dd4004087b85ff668047319dc-budget-fiscal-analyst-fines-and-fees-justice-center-new-york</t>
   </si>
   <si>
+    <t>Campaigns Director (Mass Incarceration, Criminal Justice, Policing)</t>
+  </si>
+  <si>
+    <t>VOCAL-NY</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21427863be8a40b0a7c7ed61b7bae56b-campaigns-director-mass-incarceration-criminal-justice-policing-vocal-ny-kings-county</t>
+  </si>
+  <si>
     <t>Chief Executive Officer</t>
   </si>
   <si>
@@ -427,6 +544,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/019edf0622fe442fabb9bb6289e6d1eb-clinical-operations-lead-1day-sooner-brooklyn</t>
   </si>
   <si>
+    <t>Coach Mentor-Fellow (Americorps Position)</t>
+  </si>
+  <si>
+    <t>Soccer Without Borders</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 25500.00 - 25500.00/year</t>
+  </si>
+  <si>
+    <t>Sports Recreation, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d53e5622b1b44df9d19fb48d4527acc-coach-mentor-fellow-americorps-position-soccer-without-borders-oakland</t>
+  </si>
+  <si>
+    <t>Commission on Immigration - Staff Attorney 2</t>
+  </si>
+  <si>
+    <t>American Bar Association</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a1724cede1814ca5a7a65544128c8fe4-commission-on-immigration-staff-attorney-2-american-bar-association-washington</t>
+  </si>
+  <si>
+    <t>Communications and Content Specialist</t>
+  </si>
+  <si>
+    <t>Respect Together</t>
+  </si>
+  <si>
+    <t>Harrisburg, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55286.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/06f3882352434ea28f2f034ef0af1f9d-communications-and-content-specialist-respect-together-harrisburg</t>
+  </si>
+  <si>
     <t>Communications Assistant</t>
   </si>
   <si>
@@ -442,6 +607,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/728af1ef388d4ac3b288b43f17b0bd2f-communications-assistant-library-foundation-of-los-angeles-los-angeles</t>
   </si>
   <si>
+    <t>Communications Director</t>
+  </si>
+  <si>
+    <t>Faith in Place</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 86100.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6caa22df3b994a489ee981416ff95011-communications-director-faith-in-place-chicago</t>
+  </si>
+  <si>
     <t>Communications Manager (Contractor)</t>
   </si>
   <si>
@@ -475,6 +658,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/d79914a2de5c408393ac8a3e9f0eb39d-community-food-program-associate-a-place-to-turn-natick</t>
   </si>
   <si>
+    <t>Community Programs Assistant (II)</t>
+  </si>
+  <si>
+    <t>Tree House Humane Society</t>
+  </si>
+  <si>
+    <t>USD 17.00 - 19.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/058d0acbe79b4440a7b1f3260a527fb8-community-programs-assistant-ii-tree-house-humane-society-chicago</t>
+  </si>
+  <si>
+    <t>Consultant (International Fisheries Data Collection / Information System Expert)</t>
+  </si>
+  <si>
+    <t>WorldFish</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ad3e67c36ea4c7192f42040d225e9d1-consultant-international-fisheries-data-collection-information-system-expert-worldfish-bayan-lepas</t>
+  </si>
+  <si>
+    <t>COORDINADOR/A DE OPERACIONES DE EMERGENCIA</t>
+  </si>
+  <si>
+    <t>Cruz Roja Argentina</t>
+  </si>
+  <si>
+    <t>ARS 1.00 - 1.00/month</t>
+  </si>
+  <si>
+    <t>Victim Support, Disaster Relief</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/447ea05f71b242ff8506b5d434be7ab8-coordinadora-de-operaciones-de-emergencia-cruz-roja-argentina-buenos-aires</t>
+  </si>
+  <si>
     <t>Data and Evaluation Coordinator</t>
   </si>
   <si>
@@ -499,9 +721,6 @@
     <t>Minnesota Center for Environmental Advocacy</t>
   </si>
   <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 31.25 - 33.65/hour</t>
   </si>
   <si>
@@ -511,6 +730,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/5c5a21c27390485f8e512de54faefc3f-data-center-associate-minnesota-center-for-environmental-advocacy-saint-paul</t>
   </si>
   <si>
+    <t>Deputy Director</t>
+  </si>
+  <si>
+    <t>Oregon Human Development Corporation</t>
+  </si>
+  <si>
+    <t>Hood River, Oregon</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f3ca2f45f14045c9a7565e4e1f56ace2-deputy-director-oregon-human-development-corporation-hood-river</t>
+  </si>
+  <si>
+    <t>Gresham, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/deff2d2b52cc4f88a3e6f4b829b5ef7b-deputy-director-oregon-human-development-corporation-gresham</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>The Trail Conservancy</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ceaa50180feb4cc2b4cccf439f1ad072-development-coordinator-the-trail-conservancy-austin</t>
+  </si>
+  <si>
     <t>Development Coordinator Donor Relations</t>
   </si>
   <si>
@@ -544,6 +802,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/4bd1e3668c9140028bfe81d42b2e3a8d-development-director-ironbound-community-corporation-of-newark-nj-newark</t>
   </si>
   <si>
+    <t>Cystic Fibrosis Foundation - Cff.org</t>
+  </si>
+  <si>
+    <t>Troy, Michigan</t>
+  </si>
+  <si>
+    <t>USD 81800.00 - 92070.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science, Community Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2ce6a46d817e4cd68d2ddfcabf0342fa-development-director-cystic-fibrosis-foundation-cfforg-troy</t>
+  </si>
+  <si>
     <t>Development Manager</t>
   </si>
   <si>
@@ -556,6 +829,69 @@
     <t>https://www.idealist.org/en/nonprofit-job/3e55137905ca4ac6bdc996cd81ed995b-development-manager-uncf-washington</t>
   </si>
   <si>
+    <t>Schoke Jewish Family Service</t>
+  </si>
+  <si>
+    <t>Stamford, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/092a46c7271c4f499a51c19c9a646868-development-manager-schoke-jewish-family-service-stamford</t>
+  </si>
+  <si>
+    <t>Development Manager (On-Site)</t>
+  </si>
+  <si>
+    <t>Young People's Chorus of NYC</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3808eb749b374d20a69330c1580f35aa-development-manager-on-site-young-peoples-chorus-of-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Development Marketing &amp; Communications Director</t>
+  </si>
+  <si>
+    <t>Dave Thomas Foundation for Adoption</t>
+  </si>
+  <si>
+    <t>Dublin, Ohio</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35cf906c6f504458837f267ebf1db0e0-development-marketing-communications-director-dave-thomas-foundation-for-adoption-dublin</t>
+  </si>
+  <si>
+    <t>Development Operations Assistant</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 34.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f3dfe8a873ae40b8ab44fdb45671c49a-development-operations-assistant-the-choice-inc-washington</t>
+  </si>
+  <si>
     <t>Director of Asset Management</t>
   </si>
   <si>
@@ -613,6 +949,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/687f2a5b8a0941afa31eb20f737f80f7-director-of-development-and-communications-custom-collaborative-new-york</t>
   </si>
   <si>
+    <t>Director of Development, College of Nursing</t>
+  </si>
+  <si>
+    <t>University of New Mexico Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>Albuquerque, New Mexico</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/82a80a4f076b40bf805c8badca14bfae-director-of-development-college-of-nursing-university-of-new-mexico-foundation-inc-albuquerque</t>
+  </si>
+  <si>
+    <t>Director of Finance &amp; Accounting</t>
+  </si>
+  <si>
+    <t>Ronald McDonald House New York</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Travel Hospitality, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/204da50f4a5641af9dcaf7c912da4a47-director-of-finance-accounting-ronald-mcdonald-house-new-york-new-york</t>
+  </si>
+  <si>
     <t>Director of HR &amp; Culture</t>
   </si>
   <si>
@@ -646,18 +1015,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/27139b31621e4091a165c7682a64a27c-director-of-operations-the-hr-source-prince-georges-county</t>
   </si>
   <si>
+    <t>Director of Professional Development</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c16ecf9b4d384eefad7defc166f20a2a-director-of-professional-development-american-association-of-community-colleges-washington</t>
+  </si>
+  <si>
     <t>Director of Programs</t>
   </si>
   <si>
-    <t>USD 70000.00 - 80000.00/year</t>
-  </si>
-  <si>
     <t>Health Medicine, Philanthropy, Women</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/bb5ba070867845998e1b57e7f77f5688-director-of-programs-the-hr-source-prince-georges-county</t>
   </si>
   <si>
+    <t>Groundswell Community Mural Project</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4e3a722c062a47738a504411ede40df7-director-of-programs-groundswell-community-mural-project-kings-county</t>
+  </si>
+  <si>
     <t>Director of Real Estate and Asset Management</t>
   </si>
   <si>
@@ -703,6 +1090,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/bce64aa388e94e05ac87a9ce56cbe4c6-director-institutional-giving-repair-the-world-new-york</t>
   </si>
   <si>
+    <t>Donor Communications Manager</t>
+  </si>
+  <si>
+    <t>Sonoma Land Trust</t>
+  </si>
+  <si>
+    <t>Santa Rosa, California</t>
+  </si>
+  <si>
+    <t>USD 98000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc1572352c724b96b55c02b0bb79d3f7-donor-communications-manager-sonoma-land-trust-santa-rosa</t>
+  </si>
+  <si>
+    <t>Eastern Region Business Representative</t>
+  </si>
+  <si>
+    <t>International Cinematographers Guild, Local 600, IATSE</t>
+  </si>
+  <si>
+    <t>USD 67531.00 - 106923.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87bc4a010ad041348f44b68c1ecf030c-eastern-region-business-representative-international-cinematographers-guild-local-600-iatse-new-york</t>
+  </si>
+  <si>
     <t>Education Coordinator</t>
   </si>
   <si>
@@ -721,6 +1141,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/f5361f81e4d6421293ec4e5464eea594-education-coordinator-neponset-river-watershed-association-canton</t>
   </si>
   <si>
+    <t>Education Reporter</t>
+  </si>
+  <si>
+    <t>CalMatters</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e7103f6437924c0bb048232a5383413b-education-reporter-calmatters-sacramento</t>
+  </si>
+  <si>
+    <t>Elementary Educator - 2026-2027 School Year - RELOCATION SUPPORT OFFERED!</t>
+  </si>
+  <si>
+    <t>Heartwood Community School</t>
+  </si>
+  <si>
+    <t>Ridgeland, South Carolina</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/abd305ab3d7c4c1883301d69b754f904-elementary-educator-2026-2027-school-year-relocation-support-offered-heartwood-community-school-ridgeland</t>
+  </si>
+  <si>
     <t>Employment Attorney/Of Counsel</t>
   </si>
   <si>
@@ -763,9 +1216,6 @@
     <t>Ann Arbor, Michigan</t>
   </si>
   <si>
-    <t>Part Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 20.00 - 20.00/hour</t>
   </si>
   <si>
@@ -775,6 +1225,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/ccf5e92af4f64c2297bd892cb6164891-environmental-educator-ecology-center-ann-arbor-ann-arbor</t>
   </si>
   <si>
+    <t>Events Coordinator</t>
+  </si>
+  <si>
+    <t>Resilient Agency</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 2500.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8187c44da0db4a37b38f215abd7ab244-events-coordinator-resilient-agency-los-angeles</t>
+  </si>
+  <si>
+    <t>Executive Assistant to Vice President &amp; Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>Young Women's Freedom Center</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cfb137ba081b468db4b7e23a0a9e380d-executive-assistant-to-vice-president-chief-operating-officer-young-womens-freedom-center-los-angeles</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -829,9 +1312,6 @@
     <t>The DDX3X Foundation</t>
   </si>
   <si>
-    <t>USD 90000.00 - 110000.00/year</t>
-  </si>
-  <si>
     <t>Children Youth, Disability, Health Medicine</t>
   </si>
   <si>
@@ -847,12 +1327,60 @@
     <t>USD 85000.00 - 100000.00/year</t>
   </si>
   <si>
-    <t>Arts Music, Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/05662c6a13254fc99b349d5d8f5ace1f-facilities-director-kaufman-music-center-new-york</t>
   </si>
   <si>
+    <t>Family Law Attorney</t>
+  </si>
+  <si>
+    <t>South Asian Network (SAN)</t>
+  </si>
+  <si>
+    <t>Artesia, California</t>
+  </si>
+  <si>
+    <t>Health Medicine, Immigrants Or Refugees, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/239e9c3c87e4444fbfbc8bf6f4294eb7-family-law-attorney-south-asian-network-san-artesia</t>
+  </si>
+  <si>
+    <t>Family Support Network (FSN) Director</t>
+  </si>
+  <si>
+    <t>Illinois Coalition for Immigrant and Refugee Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3e8e601da224598a533fda913168ab1-family-support-network-fsn-director-illinois-coalition-for-immigrant-and-refugee-rights-chicago</t>
+  </si>
+  <si>
+    <t>FarmSTAND Staff Attorney</t>
+  </si>
+  <si>
+    <t>FarmSTAND</t>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9215467668e7448ea12d3313323a8862-farmstand-staff-attorney-farmstand-washington</t>
+  </si>
+  <si>
+    <t>Foundation Relations Manager</t>
+  </si>
+  <si>
+    <t>Groundswell Fund</t>
+  </si>
+  <si>
+    <t>USD 101475.00 - 110495.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Reproductive Health Rights, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/245df92942b44c6984bd58c9469baf5f-foundation-relations-manager-groundswell-fund-chicago</t>
+  </si>
+  <si>
     <t>Fractional Development Director</t>
   </si>
   <si>
@@ -868,6 +1396,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/8b70f92591a64fa880940927daeb9a23-fractional-development-director-period-education-project-greenville</t>
   </si>
   <si>
+    <t>Grant Writer</t>
+  </si>
+  <si>
+    <t>Arts for Learning Maryland</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 59300.00 - 59300.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc16300dc280457eaede0aacd3259291-grant-writer-arts-for-learning-maryland-baltimore</t>
+  </si>
+  <si>
     <t>Grounds and Buildings Manager</t>
   </si>
   <si>
@@ -883,6 +1426,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c74822e4c5ab41909977ed922dfc0a67-grounds-and-buildings-manager-north10-philadelphia-philadelphia</t>
   </si>
   <si>
+    <t>Homeless Veterans Social Worker</t>
+  </si>
+  <si>
+    <t>Legal Aid Society of Eastern Virginia</t>
+  </si>
+  <si>
+    <t>Norfolk, Virginia</t>
+  </si>
+  <si>
+    <t>Disability, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fdb5b64d305f44df916201cf9a44ecc6-homeless-veterans-social-worker-legal-aid-society-of-eastern-virginia-norfolk</t>
+  </si>
+  <si>
     <t>Housing &amp; Financial Counselor</t>
   </si>
   <si>
@@ -892,6 +1450,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/a3b090cb0417405594916137e09d7953-housing-financial-counselor-housing-initiative-partnership-inc-hyattsville</t>
   </si>
   <si>
+    <t>Human Resources Business Partner - People and Culture</t>
+  </si>
+  <si>
+    <t>Do Good Multnomah</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 72103.00 - 72103.00/year</t>
+  </si>
+  <si>
+    <t>Veterans, Housing Homelessness, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e0eb6aff2570442cb8ff4e847519c7ef-human-resources-business-partner-people-and-culture-do-good-multnomah-portland</t>
+  </si>
+  <si>
+    <t>Immigration Attorney</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Immigrants Or Refugees, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/338a8f3566924e98b4473b33cd844df0-immigration-attorney-south-asian-network-san-artesia</t>
+  </si>
+  <si>
+    <t>IT Assistant - Product, Adoption and Support</t>
+  </si>
+  <si>
+    <t>World Food Programme</t>
+  </si>
+  <si>
+    <t>Panama City, Panamá Province, PA</t>
+  </si>
+  <si>
+    <t>Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e2c7106c4e441c4885c31ef92c63641-it-assistant-product-adoption-and-support-world-food-programme-panama-city</t>
+  </si>
+  <si>
+    <t>Legal Director of the Public Defense Backup Center</t>
+  </si>
+  <si>
+    <t>New York State Defenders Association, Inc.</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Crime Safety, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a3fd3085e08c4af0b6462f4ebbd297c9-legal-director-of-the-public-defense-backup-center-new-york-state-defenders-association-inc-albany</t>
+  </si>
+  <si>
     <t>Legal Fellow (Full-time)</t>
   </si>
   <si>
@@ -910,6 +1528,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/7948c28cc02a4bf18a08e5c4ba3d2c0f-legal-fellow-full-time-fair-housing-advocates-of-northern-california-san-rafael</t>
   </si>
   <si>
+    <t>Legal Operations Administrator</t>
+  </si>
+  <si>
+    <t>Earthjustice</t>
+  </si>
+  <si>
+    <t>USD 101200.00 - 132200.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8ec64c98cbbe450dafccd55d6584ebf3-legal-operations-administrator-earthjustice-san-francisco</t>
+  </si>
+  <si>
     <t>Licensed Mental Health Counselor</t>
   </si>
   <si>
@@ -970,6 +1600,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/63033d1b9e43460d85103045a8036976-manager-of-payroll-hris-operations-greater-jamaica-development-corporation-queens-county</t>
   </si>
   <si>
+    <t>Manager of Programs</t>
+  </si>
+  <si>
+    <t>Chicago Council on Science and Technology</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Science Technology, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db27596ab6ed4ca88f1815894ca27ae7-manager-of-programs-chicago-council-on-science-and-technology-chicago</t>
+  </si>
+  <si>
     <t>Manager, Direct Marketing</t>
   </si>
   <si>
@@ -988,6 +1633,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/13d83e657e6743e98ffb57e5de8980e8-manager-direct-marketing-naacp-legal-defense-and-educational-fund-inc-new-york</t>
   </si>
   <si>
+    <t>Manager, Operations and Administration</t>
+  </si>
+  <si>
+    <t>Northeast Business Group on Health</t>
+  </si>
+  <si>
+    <t>Health Medicine, Education, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7e6a792736e54fafb5f959846fd6c103-manager-operations-and-administration-northeast-business-group-on-health-new-york</t>
+  </si>
+  <si>
+    <t>Marketing Communications Coordinator</t>
+  </si>
+  <si>
+    <t>South Carolina Aquarium</t>
+  </si>
+  <si>
+    <t>Charleston, South Carolina</t>
+  </si>
+  <si>
+    <t>USD 44000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4a0eeae8edf948a5a08862e7c4f3451e-marketing-communications-coordinator-south-carolina-aquarium-charleston</t>
+  </si>
+  <si>
+    <t>Mathematics Fellow (Exponent Fellowship)</t>
+  </si>
+  <si>
+    <t>National Museum of Mathematics</t>
+  </si>
+  <si>
+    <t>USD 47000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c31f130c72434e7aa65845f69480d4de-mathematics-fellow-exponent-fellowship-national-museum-of-mathematics-new-york</t>
+  </si>
+  <si>
     <t>Membership Coordinator</t>
   </si>
   <si>
@@ -1009,6 +1699,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/002cc99c47ab4f0e97a83b6a252976bf-monitoring-evaluation-accountability-learning-meal-advisor-contract-elba-hope-foundation-new-york</t>
   </si>
   <si>
+    <t>North Suburban Organizer</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6182b54b42a04f4da2371eb425cf540d-north-suburban-organizer-illinois-coalition-for-immigrant-and-refugee-rights-chicago</t>
+  </si>
+  <si>
     <t>Office Administrator &amp; Executive Assistant (Full-time)</t>
   </si>
   <si>
@@ -1051,9 +1753,6 @@
     <t>A Place Called Home</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 27.00 - 27.00/hour</t>
   </si>
   <si>
@@ -1063,6 +1762,78 @@
     <t>https://www.idealist.org/en/nonprofit-job/bbbcba51a9f64897bc69ff7ca2fe161d-part-time-teaching-artist-music-a-place-called-home-los-angeles</t>
   </si>
   <si>
+    <t>Policy Advocacy Associate</t>
+  </si>
+  <si>
+    <t>Center for Constitutional Rights</t>
+  </si>
+  <si>
+    <t>USD 85066.00 - 110849.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/890e87ab24874f8295e49119b14c5d6c-policy-advocacy-associate-center-for-constitutional-rights-new-york</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>Center for Care Innovations</t>
+  </si>
+  <si>
+    <t>USD 58839.00 - 88259.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/106250b77261452a8611d58d5337d797-program-coordinator-center-for-care-innovations-oakland</t>
+  </si>
+  <si>
+    <t>The Tandana Foundation</t>
+  </si>
+  <si>
+    <t>Otavalo, Imbabura, EC</t>
+  </si>
+  <si>
+    <t>USD 850.00 - 1000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/91a2d169d6074084a45da29c3165e5c1-program-coordinator-the-tandana-foundation-otavalo</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>So'oh-Shinálí Sister Project</t>
+  </si>
+  <si>
+    <t>USD 33.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c14f879089b489a9dbb9df97aa3f96a-program-manager-sooh-shinali-sister-project-los-angeles</t>
+  </si>
+  <si>
+    <t>USD 76800.00 - 115200.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/911d9fe55dab4ddcaac0085b140973f5-program-manager-center-for-care-innovations-oakland</t>
+  </si>
+  <si>
+    <t>Program Operations Manager</t>
+  </si>
+  <si>
+    <t>Careers In Nonprofits, Inc.</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a9d2d07f7bd14b259804c0f8c10a1ab6-program-operations-manager-careers-in-nonprofits-inc-washington</t>
+  </si>
+  <si>
     <t>Project Manager</t>
   </si>
   <si>
@@ -1078,6 +1849,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/e5f5c92d105e4c74acc6fc5cf16f1e2c-project-manager-the-hr-source-arlington</t>
   </si>
   <si>
+    <t>Public Defense Backup Center Legal Coordinator</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 69000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/920c2b9fe57f421eb3cb91e552447f5e-public-defense-backup-center-legal-coordinator-new-york-state-defenders-association-inc-albany</t>
+  </si>
+  <si>
+    <t>Public Policy Specialist</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4fe4e6b3cc74358b1db6ef412effab3-public-policy-specialist-respect-together-harrisburg</t>
+  </si>
+  <si>
+    <t>RLC Field Sales Representative (Boston, MA)</t>
+  </si>
+  <si>
+    <t>Rescuing Leftover Cuisine</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6fe1e25c93614f19ac56c82b1cd3bc51-rlc-field-sales-representative-boston-ma-rescuing-leftover-cuisine-boston</t>
+  </si>
+  <si>
+    <t>Senior Associate, External Engagement</t>
+  </si>
+  <si>
+    <t>SPEND Initiative</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/532631e8c2574ddcba60bff212a891ef-senior-associate-external-engagement-spend-initiative-watertown</t>
+  </si>
+  <si>
     <t>Senior Director of Digital Communications</t>
   </si>
   <si>
@@ -1087,6 +1903,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/da8bc786fea543eb85120f3e7644a043-senior-director-of-digital-communications-reproductive-freedom-for-all-washington</t>
   </si>
   <si>
+    <t>Senior Manager, Operations &amp; HR</t>
+  </si>
+  <si>
+    <t>Intentional Philanthropy</t>
+  </si>
+  <si>
+    <t>Bethesda, Maryland</t>
+  </si>
+  <si>
+    <t>USD 73500.00 - 98000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/6b9a414543f34a1686c25a1ba9115219-senior-manager-operations-hr-intentional-philanthropy-bethesda</t>
+  </si>
+  <si>
+    <t>Senior Policy Advisor, Family Policy</t>
+  </si>
+  <si>
+    <t>Third Way</t>
+  </si>
+  <si>
+    <t>USD 84000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6745690c6e1a4457af166306d7b1bb56-senior-policy-advisor-family-policy-third-way-washington</t>
+  </si>
+  <si>
+    <t>Senior Policy Advisor, Fusion Energy</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc81e48fda614f7185abc5df83053c89-senior-policy-advisor-fusion-energy-third-way-washington</t>
+  </si>
+  <si>
+    <t>Senior Vice President, Partnerships, Ventures &amp; Innovation</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d5284b55a994ef2890bf971e4dcd8c5-senior-vice-president-partnerships-ventures-innovation-american-association-of-community-colleges-washington</t>
+  </si>
+  <si>
     <t>Social Media Campaign Strategist/Senior Strategist</t>
   </si>
   <si>
@@ -1102,6 +1966,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/10ad03c49a214835b0cc81cee32b4f49-social-media-campaign-strategistsenior-strategist-human-rights-first-new-york</t>
   </si>
   <si>
+    <t>Special Events Associate</t>
+  </si>
+  <si>
+    <t>Center for American Progress</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 66700.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Media, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28b5f56a31304c749ae31dee0524c2a7-special-events-associate-center-for-american-progress-washington</t>
+  </si>
+  <si>
     <t>Specialist, Assessment</t>
   </si>
   <si>
@@ -1114,6 +1993,21 @@
     <t>https://www.idealist.org/en/job/aabd17f60e28463da56b2edd08713e7d-specialist-assessment-chef-ann-foundation-boulder</t>
   </si>
   <si>
+    <t>Sr. Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>KABOOM!</t>
+  </si>
+  <si>
+    <t>USD 27.58 - 29.93/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Race Ethnicity, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4e531a170e9846c18458641fb6d594c8-sr-administrative-coordinator-kaboom-bethesda</t>
+  </si>
+  <si>
     <t>Staff Accountant</t>
   </si>
   <si>
@@ -1132,6 +2026,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/0e2725a1aedc4318a5b686f5342eda31-staff-attorney-fair-housing-advocates-of-northern-california-san-rafael</t>
   </si>
   <si>
+    <t>Tahirih Justice Center</t>
+  </si>
+  <si>
+    <t>San Bruno, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 99000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/132569aededd4405a4147550a8c6a0d8-staff-attorney-tahirih-justice-center-san-bruno</t>
+  </si>
+  <si>
     <t>Staff Attorney I or II</t>
   </si>
   <si>
@@ -1147,6 +2056,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/d00e27039fba414b84c5a3dfb37f7395-staff-attorney-i-or-ii-garment-worker-center-los-angeles</t>
   </si>
   <si>
+    <t>Substitute Preschool Associate Teacher</t>
+  </si>
+  <si>
+    <t>KidWorks</t>
+  </si>
+  <si>
+    <t>Santa Ana, California</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac24c5405e74442ebd7a5695eab2914a-substitute-preschool-associate-teacher-kidworks-santa-ana</t>
+  </si>
+  <si>
+    <t>Temporary Editorial Assistant, Knowable Magazine (Remote)</t>
+  </si>
+  <si>
+    <t>Annual Reviews</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 25.64 - 32.82/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49eab9ff3d7a4d9d9247c048e3016e21-temporary-editorial-assistant-knowable-magazine-remote-annual-reviews-san-mateo</t>
+  </si>
+  <si>
     <t>Temporary Rental Assistance Program Coordinator</t>
   </si>
   <si>
@@ -1159,6 +2098,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/0dab0c22d8af420aaa5d8c37d5d2cce6-temporary-rental-assistance-program-coordinator-housing-rights-center-los-angeles</t>
   </si>
   <si>
+    <t>Upkeep and Repair Manager</t>
+  </si>
+  <si>
+    <t>Housing Opportunities and Maintenance for the Elderly (H.O.M.E.)</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1701042ed03f483ca84d187c0a5c1eac-upkeep-and-repair-manager-housing-opportunities-and-maintenance-for-the-elderly-home-chicago</t>
+  </si>
+  <si>
     <t>User Support Technician I</t>
   </si>
   <si>
@@ -1172,6 +2123,453 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/bd81b8fd75f14c0fa6fc114d23062256-user-support-technician-i-central-park-conservancy-new-york</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE SUPPORT ASSOCIATE</t>
+  </si>
+  <si>
+    <t>PASA Sustainable Agriculture</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73009291</t>
+  </si>
+  <si>
+    <t>AGENT ASSOCIATE</t>
+  </si>
+  <si>
+    <t>AGRICULTURE AND FOOD SYSTEMS - University of Maryland Extension</t>
+  </si>
+  <si>
+    <t>Clinton, Maryland</t>
+  </si>
+  <si>
+    <t>Program Operations</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72993405</t>
+  </si>
+  <si>
+    <t>AGRICULTURE PROJECTS COORDINATOR</t>
+  </si>
+  <si>
+    <t>Alliance for the Chesapeake Bay</t>
+  </si>
+  <si>
+    <t>Lancaster County, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72972631</t>
+  </si>
+  <si>
+    <t>CHIEF OPERATING OFFICER</t>
+  </si>
+  <si>
+    <t>Farmlink</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73001959</t>
+  </si>
+  <si>
+    <t>COLLECTIVE SALES MANAGER</t>
+  </si>
+  <si>
+    <t>Farm Alliance of Baltimore</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72995849</t>
+  </si>
+  <si>
+    <t>COMMUNICATIONS AND MARKETING MANAGER</t>
+  </si>
+  <si>
+    <t>Worcester County Food Bank</t>
+  </si>
+  <si>
+    <t>Worcester County, Massachusetts</t>
+  </si>
+  <si>
+    <t>Communications &amp; Outreach</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73006847</t>
+  </si>
+  <si>
+    <t>COMPOST COORDINATOR</t>
+  </si>
+  <si>
+    <t>George Mason University</t>
+  </si>
+  <si>
+    <t>Fairfax, Virginia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72968965</t>
+  </si>
+  <si>
+    <t>COORDINATOR</t>
+  </si>
+  <si>
+    <t>FOOD RECOVERY PROGRAM - Spoonfuls</t>
+  </si>
+  <si>
+    <t>Framingham, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73019067</t>
+  </si>
+  <si>
+    <t>DATA STEWARDSHIP AND REPORTING COORDINATOR</t>
+  </si>
+  <si>
+    <t>Practical Farmers of Iowa</t>
+  </si>
+  <si>
+    <t>Ames, Iowa</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73003181</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT AND COMMUNICATIONS MANAGER</t>
+  </si>
+  <si>
+    <t>Savanna Institute</t>
+  </si>
+  <si>
+    <t>Fund Development</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72986073</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT COORDINATOR</t>
+  </si>
+  <si>
+    <t>Common Ground Farm</t>
+  </si>
+  <si>
+    <t>Beacon, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72987295</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73005625</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF BUSINESS DEVELOPMENT</t>
+  </si>
+  <si>
+    <t>Agency 29</t>
+  </si>
+  <si>
+    <t>Hybrid in Rochester, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72978741</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF CORPORATE</t>
+  </si>
+  <si>
+    <t>CAMPAIGN AND INSTITUTIONAL GIVING - Second Harvest Heartland</t>
+  </si>
+  <si>
+    <t>Brooklyn Park, Minnesota</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72979963</t>
+  </si>
+  <si>
+    <t>EMERGING CONTAMINANTS OUTREACH SPECIALIST</t>
+  </si>
+  <si>
+    <t>University of Wisconsin</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72999515</t>
+  </si>
+  <si>
+    <t>EQUITY INCLUSION AND COMMUNITY ENGAGEMENT MANAGER</t>
+  </si>
+  <si>
+    <t>National Coop Grocers</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72977519</t>
+  </si>
+  <si>
+    <t>EXECUTIVE ASSISTANT</t>
+  </si>
+  <si>
+    <t>Food and Friends</t>
+  </si>
+  <si>
+    <t>Washington DC, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72967743</t>
+  </si>
+  <si>
+    <t>FARMER GRANT ADMINISTRATOR</t>
+  </si>
+  <si>
+    <t>Northeast Sustainable Agriculture Research and Education</t>
+  </si>
+  <si>
+    <t>South Burlington, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72973853</t>
+  </si>
+  <si>
+    <t>FINANCE AND OPERATIONS SENIOR DIRECTOR</t>
+  </si>
+  <si>
+    <t>Sustainable Agriculture and Food Systems Funders</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73016623</t>
+  </si>
+  <si>
+    <t>FINANCE DIRECTOR</t>
+  </si>
+  <si>
+    <t>MAD Agriculture</t>
+  </si>
+  <si>
+    <t>Remote with a preference for Boulder, CO, Remote</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72981185</t>
+  </si>
+  <si>
+    <t>FINANCE MANAGER</t>
+  </si>
+  <si>
+    <t>BOOKKEEPER - Heartland Fund</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72982407</t>
+  </si>
+  <si>
+    <t>FOOD SOURCING MANAGER</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73004403</t>
+  </si>
+  <si>
+    <t>LIVESTOCK ASSISTANT</t>
+  </si>
+  <si>
+    <t>Heifer USA</t>
+  </si>
+  <si>
+    <t>Perryville, Arkansas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72965299</t>
+  </si>
+  <si>
+    <t>NORTH SHORE DIRT CREW CO-SUPERVISOR</t>
+  </si>
+  <si>
+    <t>The Food Project</t>
+  </si>
+  <si>
+    <t>Hybrid in Lynn and Wenham, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72990961</t>
+  </si>
+  <si>
+    <t>PACKAGING COORDINATOR</t>
+  </si>
+  <si>
+    <t>King Arthur Baking Company</t>
+  </si>
+  <si>
+    <t>White River Junction, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72998293</t>
+  </si>
+  <si>
+    <t>PARTNER ADVOCATE</t>
+  </si>
+  <si>
+    <t>FoodWorks</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72970187</t>
+  </si>
+  <si>
+    <t>PARTNER LIASON</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73010513</t>
+  </si>
+  <si>
+    <t>PARTNERSHIP INTAKE COORDINATOR</t>
+  </si>
+  <si>
+    <t>Canadian Food Innovation Network</t>
+  </si>
+  <si>
+    <t>Guelph, Ontario</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72994627</t>
+  </si>
+  <si>
+    <t>PRINCIPAL</t>
+  </si>
+  <si>
+    <t>ADVISORY SERVICES - SNAP POLICY - Mathematica</t>
+  </si>
+  <si>
+    <t>Policy &amp; Advocacy</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73000737</t>
+  </si>
+  <si>
+    <t>PROGRAM IMPACT DATA MANAGER</t>
+  </si>
+  <si>
+    <t>Reinvestment Fund</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73012957</t>
+  </si>
+  <si>
+    <t>PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>FOOD AND FARMING STORYTELLING FUND - Sentient</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72976297</t>
+  </si>
+  <si>
+    <t>HEALING HARVEST - Darmouth Cancer Center</t>
+  </si>
+  <si>
+    <t>Lebanon, New Hampshire</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72988517</t>
+  </si>
+  <si>
+    <t>HEALTH CARE - AI - PARTNERSHIPS AND PRODUCT SOLUTIONS FOR SUSTAINABLE FOOD SYSTEMS - American Heart Association</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73014179</t>
+  </si>
+  <si>
+    <t>RECRUITMENT AND OUTREACH MANAGER</t>
+  </si>
+  <si>
+    <t>New Roots Institute</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72983629</t>
+  </si>
+  <si>
+    <t>REGENERATIVE AGRICULTURE LEAD</t>
+  </si>
+  <si>
+    <t>PUR</t>
+  </si>
+  <si>
+    <t>Hybrid in Toronto, Ontario</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73017845</t>
+  </si>
+  <si>
+    <t>RESEARCH COORDINATOR</t>
+  </si>
+  <si>
+    <t>Teaching Kitchen Collaborative</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73015401</t>
+  </si>
+  <si>
+    <t>ROADSIDE STORE AND CAFE</t>
+  </si>
+  <si>
+    <t>WORK TEAM LEADER - Gould Farm</t>
+  </si>
+  <si>
+    <t>Monterey, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72989739</t>
+  </si>
+  <si>
+    <t>SENIOR CLIMATE AND SOIL HEALTH SCIENTIST</t>
+  </si>
+  <si>
+    <t>American Farmland Trust</t>
+  </si>
+  <si>
+    <t>Remote, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72984851</t>
+  </si>
+  <si>
+    <t>SENIOR PARTNER SERVICES ADVISOR</t>
+  </si>
+  <si>
+    <t>Second Harvest Heartland</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73008069</t>
+  </si>
+  <si>
+    <t>SPECIALIST</t>
+  </si>
+  <si>
+    <t>ASSESSMENT - Chef Ann Foundation</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72997071</t>
+  </si>
+  <si>
+    <t>SR DIRECTOR</t>
+  </si>
+  <si>
+    <t>North Dakota Farmers Union Foundation</t>
+  </si>
+  <si>
+    <t>Bismarck, North Dakota</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72992183</t>
   </si>
 </sst>
 </file>
@@ -1557,7 +2955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -1653,59 +3051,59 @@
         <v>24</v>
       </c>
       <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" t="s">
+      <c r="E6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
         <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>36</v>
@@ -1722,16 +3120,39 @@
         <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
         <v>40</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>41</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1743,6 +3164,7 @@
     <hyperlink ref="H5" r:id="rId4"/>
     <hyperlink ref="H6" r:id="rId5"/>
     <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1799,7 +3221,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -1840,367 +3262,367 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F14" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F15" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F16" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" t="s">
+        <v>124</v>
+      </c>
+      <c r="F17" t="s">
         <v>128</v>
-      </c>
-      <c r="D17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" t="s">
-        <v>129</v>
-      </c>
-      <c r="F17" t="s">
-        <v>130</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>131</v>
@@ -2214,355 +3636,355 @@
         <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="E18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F19" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="F19" t="s">
-        <v>140</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="F20" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" t="s">
+        <v>145</v>
+      </c>
+      <c r="F21" t="s">
+        <v>146</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="B21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C21" t="s">
-        <v>149</v>
-      </c>
-      <c r="D21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" t="s">
-        <v>150</v>
-      </c>
-      <c r="F21" t="s">
-        <v>151</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C22" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E22" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F22" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C23" t="s">
         <v>155</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="E23" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F23" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C24" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D24" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E24" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F24" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C25" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" t="s">
+        <v>168</v>
+      </c>
+      <c r="F25" t="s">
+        <v>169</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="B25" t="s">
-        <v>171</v>
-      </c>
-      <c r="C25" t="s">
-        <v>172</v>
-      </c>
-      <c r="D25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" t="s">
-        <v>173</v>
-      </c>
-      <c r="F25" t="s">
-        <v>174</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F26" t="s">
-        <v>104</v>
+        <v>174</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" t="s">
+        <v>178</v>
+      </c>
+      <c r="D27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" t="s">
+        <v>179</v>
+      </c>
+      <c r="F27" t="s">
         <v>180</v>
       </c>
-      <c r="B27" t="s">
+      <c r="H27" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="C27" t="s">
-        <v>182</v>
-      </c>
-      <c r="D27" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" t="s">
-        <v>183</v>
-      </c>
-      <c r="F27" t="s">
-        <v>184</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E28" t="s">
-        <v>187</v>
+        <v>61</v>
       </c>
       <c r="F28" t="s">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" t="s">
         <v>189</v>
       </c>
-      <c r="B29" t="s">
+      <c r="F29" t="s">
         <v>190</v>
       </c>
-      <c r="C29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="H29" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="F29" t="s">
-        <v>192</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>192</v>
+      </c>
+      <c r="B30" t="s">
+        <v>193</v>
+      </c>
+      <c r="C30" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" t="s">
         <v>194</v>
       </c>
-      <c r="B30" t="s">
+      <c r="F30" t="s">
         <v>195</v>
       </c>
-      <c r="C30" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" t="s">
-        <v>54</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="H30" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="F30" t="s">
-        <v>197</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" t="s">
         <v>199</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D31" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" t="s">
         <v>200</v>
       </c>
-      <c r="C31" t="s">
+      <c r="F31" t="s">
         <v>201</v>
       </c>
-      <c r="D31" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="H31" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="F31" t="s">
-        <v>203</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" t="s">
+        <v>204</v>
+      </c>
+      <c r="C32" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" t="s">
         <v>205</v>
       </c>
-      <c r="B32" t="s">
+      <c r="F32" t="s">
         <v>206</v>
       </c>
-      <c r="C32" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" t="s">
-        <v>54</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="H32" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="F32" t="s">
-        <v>208</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" t="s">
         <v>210</v>
       </c>
-      <c r="B33" t="s">
-        <v>206</v>
-      </c>
-      <c r="C33" t="s">
-        <v>116</v>
-      </c>
       <c r="D33" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E33" t="s">
         <v>211</v>
@@ -2582,870 +4004,2457 @@
         <v>215</v>
       </c>
       <c r="C34" t="s">
+        <v>199</v>
+      </c>
+      <c r="D34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" t="s">
         <v>216</v>
       </c>
-      <c r="D34" t="s">
-        <v>54</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>61</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="F34" t="s">
-        <v>218</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>218</v>
+      </c>
+      <c r="B35" t="s">
+        <v>219</v>
+      </c>
+      <c r="C35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" t="s">
         <v>220</v>
       </c>
-      <c r="B35" t="s">
+      <c r="H35" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="C35" t="s">
-        <v>116</v>
-      </c>
-      <c r="D35" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" t="s">
-        <v>74</v>
-      </c>
-      <c r="F35" t="s">
-        <v>222</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>222</v>
+      </c>
+      <c r="B36" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" t="s">
+        <v>96</v>
+      </c>
+      <c r="D36" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" t="s">
         <v>224</v>
       </c>
-      <c r="B36" t="s">
+      <c r="F36" t="s">
         <v>225</v>
       </c>
-      <c r="C36" t="s">
-        <v>116</v>
-      </c>
-      <c r="D36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="H36" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="F36" t="s">
-        <v>227</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>227</v>
+      </c>
+      <c r="B37" t="s">
+        <v>228</v>
+      </c>
+      <c r="C37" t="s">
         <v>229</v>
       </c>
-      <c r="B37" t="s">
+      <c r="D37" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" t="s">
         <v>230</v>
       </c>
-      <c r="C37" t="s">
+      <c r="F37" t="s">
         <v>231</v>
       </c>
-      <c r="D37" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="H37" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="F37" t="s">
-        <v>233</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>233</v>
+      </c>
+      <c r="B38" t="s">
+        <v>234</v>
+      </c>
+      <c r="C38" t="s">
+        <v>229</v>
+      </c>
+      <c r="D38" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38" t="s">
         <v>235</v>
       </c>
-      <c r="B38" t="s">
+      <c r="F38" t="s">
         <v>236</v>
       </c>
-      <c r="C38" t="s">
+      <c r="H38" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="D38" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" t="s">
-        <v>238</v>
-      </c>
-      <c r="F38" t="s">
-        <v>239</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>238</v>
+      </c>
+      <c r="B39" t="s">
+        <v>239</v>
+      </c>
+      <c r="C39" t="s">
+        <v>240</v>
+      </c>
+      <c r="D39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" t="s">
         <v>241</v>
       </c>
-      <c r="B39" t="s">
+      <c r="F39" t="s">
         <v>242</v>
       </c>
-      <c r="C39" t="s">
-        <v>128</v>
-      </c>
-      <c r="D39" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="H39" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="F39" t="s">
-        <v>244</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B40" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C40" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D40" t="s">
-        <v>249</v>
+        <v>60</v>
       </c>
       <c r="E40" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="F40" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B41" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C41" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D41" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E41" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="F41" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>251</v>
+      </c>
+      <c r="B42" t="s">
+        <v>252</v>
+      </c>
+      <c r="C42" t="s">
         <v>253</v>
       </c>
-      <c r="B42" t="s">
-        <v>259</v>
-      </c>
-      <c r="C42" t="s">
-        <v>260</v>
-      </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E42" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F42" t="s">
-        <v>262</v>
+        <v>174</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B43" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C43" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E43" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F43" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B44" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>116</v>
+        <v>263</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E44" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F44" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B45" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C45" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" t="s">
+        <v>269</v>
+      </c>
+      <c r="F45" t="s">
         <v>128</v>
       </c>
-      <c r="D45" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" t="s">
-        <v>276</v>
-      </c>
-      <c r="F45" t="s">
-        <v>277</v>
-      </c>
       <c r="H45" s="2" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B46" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>272</v>
       </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E46" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="F46" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B47" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="D47" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E47" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="F47" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>282</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
+        <v>283</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E48" t="s">
-        <v>290</v>
+        <v>61</v>
       </c>
       <c r="F48" t="s">
-        <v>69</v>
+        <v>284</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B49" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C49" t="s">
-        <v>294</v>
+        <v>118</v>
       </c>
       <c r="D49" t="s">
-        <v>249</v>
+        <v>288</v>
       </c>
       <c r="E49" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="F49" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B50" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C50" t="s">
-        <v>128</v>
+        <v>294</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E50" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F50" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B51" t="s">
-        <v>304</v>
+        <v>172</v>
       </c>
       <c r="C51" t="s">
-        <v>305</v>
+        <v>84</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E51" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="F51" t="s">
-        <v>307</v>
+        <v>174</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>301</v>
+      </c>
+      <c r="B52" t="s">
+        <v>302</v>
+      </c>
+      <c r="C52" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52" t="s">
+        <v>60</v>
+      </c>
+      <c r="E52" t="s">
         <v>303</v>
       </c>
-      <c r="B52" t="s">
+      <c r="F52" t="s">
         <v>304</v>
       </c>
-      <c r="C52" t="s">
-        <v>309</v>
-      </c>
-      <c r="D52" t="s">
-        <v>54</v>
-      </c>
-      <c r="E52" t="s">
-        <v>306</v>
-      </c>
-      <c r="F52" t="s">
-        <v>307</v>
-      </c>
       <c r="H52" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B53" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C53" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D53" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E53" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F53" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>311</v>
+      </c>
+      <c r="B54" t="s">
+        <v>312</v>
+      </c>
+      <c r="C54" t="s">
+        <v>313</v>
+      </c>
+      <c r="D54" t="s">
+        <v>60</v>
+      </c>
+      <c r="E54" t="s">
+        <v>314</v>
+      </c>
+      <c r="F54" t="s">
+        <v>315</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="B54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C54" t="s">
-        <v>60</v>
-      </c>
-      <c r="D54" t="s">
-        <v>54</v>
-      </c>
-      <c r="E54" t="s">
-        <v>261</v>
-      </c>
-      <c r="F54" t="s">
-        <v>218</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>317</v>
+      </c>
+      <c r="B55" t="s">
         <v>318</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
+        <v>167</v>
+      </c>
+      <c r="D55" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55" t="s">
         <v>319</v>
       </c>
-      <c r="C55" t="s">
-        <v>94</v>
-      </c>
-      <c r="D55" t="s">
-        <v>54</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>320</v>
       </c>
-      <c r="F55" t="s">
+      <c r="H55" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B56" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C56" t="s">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="D56" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E56" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F56" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B57" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C57" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="D57" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E57" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F57" t="s">
-        <v>74</v>
+        <v>331</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B58" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C58" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E58" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F58" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B59" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="C59" t="s">
-        <v>294</v>
+        <v>84</v>
       </c>
       <c r="D59" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E59" t="s">
-        <v>332</v>
+        <v>85</v>
       </c>
       <c r="F59" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B60" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C60" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="E60" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F60" t="s">
-        <v>197</v>
+        <v>341</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B61" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C61" t="s">
-        <v>110</v>
+        <v>345</v>
       </c>
       <c r="D61" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="E61" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F61" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B62" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C62" t="s">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="D62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E62" t="s">
-        <v>346</v>
+        <v>61</v>
       </c>
       <c r="F62" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s">
-        <v>206</v>
+        <v>354</v>
       </c>
       <c r="C63" t="s">
-        <v>350</v>
+        <v>84</v>
       </c>
       <c r="D63" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E63" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F63" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>359</v>
       </c>
       <c r="C64" t="s">
-        <v>94</v>
+        <v>360</v>
       </c>
       <c r="D64" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E64" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="F64" t="s">
-        <v>96</v>
+        <v>362</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B65" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C65" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="D65" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E65" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F65" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B66" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C66" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="D66" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E66" t="s">
-        <v>74</v>
+        <v>372</v>
       </c>
       <c r="F66" t="s">
-        <v>74</v>
+        <v>373</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>376</v>
       </c>
       <c r="C67" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D67" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E67" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="F67" t="s">
-        <v>69</v>
+        <v>378</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="B68" t="s">
-        <v>293</v>
+        <v>381</v>
       </c>
       <c r="C68" t="s">
-        <v>294</v>
+        <v>382</v>
       </c>
       <c r="D68" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E68" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="F68" t="s">
-        <v>296</v>
+        <v>384</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="B69" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C69" t="s">
-        <v>345</v>
+        <v>388</v>
       </c>
       <c r="D69" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E69" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="F69" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="B70" t="s">
-        <v>339</v>
+        <v>393</v>
       </c>
       <c r="C70" t="s">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="D70" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="E70" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="F70" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="B71" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="C71" t="s">
+        <v>399</v>
+      </c>
+      <c r="D71" t="s">
+        <v>288</v>
+      </c>
+      <c r="E71" t="s">
+        <v>400</v>
+      </c>
+      <c r="F71" t="s">
+        <v>401</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>403</v>
+      </c>
+      <c r="B72" t="s">
+        <v>404</v>
+      </c>
+      <c r="C72" t="s">
+        <v>405</v>
+      </c>
+      <c r="D72" t="s">
+        <v>53</v>
+      </c>
+      <c r="E72" t="s">
+        <v>406</v>
+      </c>
+      <c r="F72" t="s">
+        <v>407</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>409</v>
+      </c>
+      <c r="B73" t="s">
+        <v>410</v>
+      </c>
+      <c r="C73" t="s">
+        <v>405</v>
+      </c>
+      <c r="D73" t="s">
+        <v>60</v>
+      </c>
+      <c r="E73" t="s">
+        <v>411</v>
+      </c>
+      <c r="F73" t="s">
+        <v>412</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>414</v>
+      </c>
+      <c r="B74" t="s">
+        <v>415</v>
+      </c>
+      <c r="C74" t="s">
+        <v>416</v>
+      </c>
+      <c r="D74" t="s">
+        <v>60</v>
+      </c>
+      <c r="E74" t="s">
+        <v>417</v>
+      </c>
+      <c r="F74" t="s">
+        <v>418</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>414</v>
+      </c>
+      <c r="B75" t="s">
+        <v>420</v>
+      </c>
+      <c r="C75" t="s">
+        <v>421</v>
+      </c>
+      <c r="D75" t="s">
+        <v>60</v>
+      </c>
+      <c r="E75" t="s">
+        <v>422</v>
+      </c>
+      <c r="F75" t="s">
+        <v>423</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>414</v>
+      </c>
+      <c r="B76" t="s">
+        <v>425</v>
+      </c>
+      <c r="C76" t="s">
+        <v>426</v>
+      </c>
+      <c r="D76" t="s">
+        <v>60</v>
+      </c>
+      <c r="E76" t="s">
+        <v>427</v>
+      </c>
+      <c r="F76" t="s">
+        <v>428</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>430</v>
+      </c>
+      <c r="B77" t="s">
+        <v>431</v>
+      </c>
+      <c r="C77" t="s">
+        <v>84</v>
+      </c>
+      <c r="D77" t="s">
+        <v>60</v>
+      </c>
+      <c r="E77" t="s">
+        <v>156</v>
+      </c>
+      <c r="F77" t="s">
+        <v>432</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>434</v>
+      </c>
+      <c r="B78" t="s">
+        <v>435</v>
+      </c>
+      <c r="C78" t="s">
+        <v>167</v>
+      </c>
+      <c r="D78" t="s">
+        <v>60</v>
+      </c>
+      <c r="E78" t="s">
+        <v>436</v>
+      </c>
+      <c r="F78" t="s">
+        <v>279</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>438</v>
+      </c>
+      <c r="B79" t="s">
+        <v>439</v>
+      </c>
+      <c r="C79" t="s">
+        <v>440</v>
+      </c>
+      <c r="D79" t="s">
+        <v>60</v>
+      </c>
+      <c r="E79" t="s">
+        <v>427</v>
+      </c>
+      <c r="F79" t="s">
+        <v>441</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>443</v>
+      </c>
+      <c r="B80" t="s">
+        <v>444</v>
+      </c>
+      <c r="C80" t="s">
+        <v>199</v>
+      </c>
+      <c r="D80" t="s">
+        <v>60</v>
+      </c>
+      <c r="E80" t="s">
+        <v>330</v>
+      </c>
+      <c r="F80" t="s">
+        <v>412</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>446</v>
+      </c>
+      <c r="B81" t="s">
+        <v>447</v>
+      </c>
+      <c r="C81" t="s">
+        <v>84</v>
+      </c>
+      <c r="D81" t="s">
+        <v>60</v>
+      </c>
+      <c r="E81" t="s">
+        <v>61</v>
+      </c>
+      <c r="F81" t="s">
+        <v>448</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>450</v>
+      </c>
+      <c r="B82" t="s">
+        <v>451</v>
+      </c>
+      <c r="C82" t="s">
+        <v>84</v>
+      </c>
+      <c r="D82" t="s">
+        <v>60</v>
+      </c>
+      <c r="E82" t="s">
+        <v>452</v>
+      </c>
+      <c r="F82" t="s">
+        <v>453</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>455</v>
+      </c>
+      <c r="B83" t="s">
+        <v>456</v>
+      </c>
+      <c r="C83" t="s">
+        <v>84</v>
+      </c>
+      <c r="D83" t="s">
+        <v>78</v>
+      </c>
+      <c r="E83" t="s">
+        <v>457</v>
+      </c>
+      <c r="F83" t="s">
+        <v>458</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>460</v>
+      </c>
+      <c r="B84" t="s">
+        <v>461</v>
+      </c>
+      <c r="C84" t="s">
+        <v>462</v>
+      </c>
+      <c r="D84" t="s">
+        <v>60</v>
+      </c>
+      <c r="E84" t="s">
+        <v>463</v>
+      </c>
+      <c r="F84" t="s">
+        <v>279</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>465</v>
+      </c>
+      <c r="B85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C85" t="s">
+        <v>106</v>
+      </c>
+      <c r="D85" t="s">
+        <v>60</v>
+      </c>
+      <c r="E85" t="s">
+        <v>467</v>
+      </c>
+      <c r="F85" t="s">
+        <v>468</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>470</v>
+      </c>
+      <c r="B86" t="s">
+        <v>471</v>
+      </c>
+      <c r="C86" t="s">
+        <v>472</v>
+      </c>
+      <c r="D86" t="s">
+        <v>60</v>
+      </c>
+      <c r="E86" t="s">
+        <v>91</v>
+      </c>
+      <c r="F86" t="s">
+        <v>473</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>475</v>
+      </c>
+      <c r="B87" t="s">
+        <v>89</v>
+      </c>
+      <c r="C87" t="s">
+        <v>90</v>
+      </c>
+      <c r="D87" t="s">
+        <v>60</v>
+      </c>
+      <c r="E87" t="s">
+        <v>476</v>
+      </c>
+      <c r="F87" t="s">
+        <v>92</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>478</v>
+      </c>
+      <c r="B88" t="s">
+        <v>479</v>
+      </c>
+      <c r="C88" t="s">
+        <v>480</v>
+      </c>
+      <c r="D88" t="s">
+        <v>60</v>
+      </c>
+      <c r="E88" t="s">
+        <v>481</v>
+      </c>
+      <c r="F88" t="s">
+        <v>482</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>484</v>
+      </c>
+      <c r="B89" t="s">
+        <v>439</v>
+      </c>
+      <c r="C89" t="s">
+        <v>440</v>
+      </c>
+      <c r="D89" t="s">
+        <v>60</v>
+      </c>
+      <c r="E89" t="s">
+        <v>427</v>
+      </c>
+      <c r="F89" t="s">
+        <v>485</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>487</v>
+      </c>
+      <c r="B90" t="s">
+        <v>488</v>
+      </c>
+      <c r="C90" t="s">
+        <v>489</v>
+      </c>
+      <c r="D90" t="s">
+        <v>60</v>
+      </c>
+      <c r="E90" t="s">
+        <v>61</v>
+      </c>
+      <c r="F90" t="s">
+        <v>490</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>492</v>
+      </c>
+      <c r="B91" t="s">
+        <v>493</v>
+      </c>
+      <c r="C91" t="s">
+        <v>494</v>
+      </c>
+      <c r="D91" t="s">
+        <v>60</v>
+      </c>
+      <c r="E91" t="s">
+        <v>495</v>
+      </c>
+      <c r="F91" t="s">
+        <v>496</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>498</v>
+      </c>
+      <c r="B92" t="s">
+        <v>499</v>
+      </c>
+      <c r="C92" t="s">
+        <v>500</v>
+      </c>
+      <c r="D92" t="s">
+        <v>288</v>
+      </c>
+      <c r="E92" t="s">
+        <v>501</v>
+      </c>
+      <c r="F92" t="s">
+        <v>502</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>504</v>
+      </c>
+      <c r="B93" t="s">
+        <v>505</v>
+      </c>
+      <c r="C93" t="s">
+        <v>84</v>
+      </c>
+      <c r="D93" t="s">
+        <v>60</v>
+      </c>
+      <c r="E93" t="s">
+        <v>506</v>
+      </c>
+      <c r="F93" t="s">
+        <v>61</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>508</v>
+      </c>
+      <c r="B94" t="s">
+        <v>509</v>
+      </c>
+      <c r="C94" t="s">
+        <v>167</v>
+      </c>
+      <c r="D94" t="s">
+        <v>60</v>
+      </c>
+      <c r="E94" t="s">
+        <v>510</v>
+      </c>
+      <c r="F94" t="s">
+        <v>511</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>513</v>
+      </c>
+      <c r="B95" t="s">
+        <v>514</v>
+      </c>
+      <c r="C95" t="s">
+        <v>515</v>
+      </c>
+      <c r="D95" t="s">
+        <v>60</v>
+      </c>
+      <c r="E95" t="s">
+        <v>516</v>
+      </c>
+      <c r="F95" t="s">
+        <v>517</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>513</v>
+      </c>
+      <c r="B96" t="s">
+        <v>514</v>
+      </c>
+      <c r="C96" t="s">
+        <v>519</v>
+      </c>
+      <c r="D96" t="s">
+        <v>60</v>
+      </c>
+      <c r="E96" t="s">
+        <v>516</v>
+      </c>
+      <c r="F96" t="s">
+        <v>517</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>521</v>
+      </c>
+      <c r="B97" t="s">
+        <v>522</v>
+      </c>
+      <c r="C97" t="s">
+        <v>161</v>
+      </c>
+      <c r="D97" t="s">
+        <v>60</v>
+      </c>
+      <c r="E97" t="s">
+        <v>523</v>
+      </c>
+      <c r="F97" t="s">
+        <v>524</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>526</v>
+      </c>
+      <c r="B98" t="s">
+        <v>344</v>
+      </c>
+      <c r="C98" t="s">
+        <v>77</v>
+      </c>
+      <c r="D98" t="s">
+        <v>60</v>
+      </c>
+      <c r="E98" t="s">
+        <v>422</v>
+      </c>
+      <c r="F98" t="s">
+        <v>347</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>528</v>
+      </c>
+      <c r="B99" t="s">
+        <v>529</v>
+      </c>
+      <c r="C99" t="s">
+        <v>199</v>
+      </c>
+      <c r="D99" t="s">
+        <v>60</v>
+      </c>
+      <c r="E99" t="s">
+        <v>530</v>
+      </c>
+      <c r="F99" t="s">
+        <v>531</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>533</v>
+      </c>
+      <c r="B100" t="s">
+        <v>534</v>
+      </c>
+      <c r="C100" t="s">
+        <v>118</v>
+      </c>
+      <c r="D100" t="s">
+        <v>60</v>
+      </c>
+      <c r="E100" t="s">
+        <v>535</v>
+      </c>
+      <c r="F100" t="s">
+        <v>536</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>533</v>
+      </c>
+      <c r="B101" t="s">
+        <v>534</v>
+      </c>
+      <c r="C101" t="s">
+        <v>167</v>
+      </c>
+      <c r="D101" t="s">
+        <v>60</v>
+      </c>
+      <c r="E101" t="s">
+        <v>535</v>
+      </c>
+      <c r="F101" t="s">
+        <v>536</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>539</v>
+      </c>
+      <c r="B102" t="s">
+        <v>540</v>
+      </c>
+      <c r="C102" t="s">
+        <v>167</v>
+      </c>
+      <c r="D102" t="s">
+        <v>60</v>
+      </c>
+      <c r="E102" t="s">
+        <v>230</v>
+      </c>
+      <c r="F102" t="s">
+        <v>541</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>543</v>
+      </c>
+      <c r="B103" t="s">
+        <v>544</v>
+      </c>
+      <c r="C103" t="s">
+        <v>545</v>
+      </c>
+      <c r="D103" t="s">
+        <v>60</v>
+      </c>
+      <c r="E103" t="s">
+        <v>546</v>
+      </c>
+      <c r="F103" t="s">
+        <v>547</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>549</v>
+      </c>
+      <c r="B104" t="s">
+        <v>550</v>
+      </c>
+      <c r="C104" t="s">
+        <v>167</v>
+      </c>
+      <c r="D104" t="s">
+        <v>134</v>
+      </c>
+      <c r="E104" t="s">
+        <v>551</v>
+      </c>
+      <c r="F104" t="s">
+        <v>552</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>554</v>
+      </c>
+      <c r="B105" t="s">
+        <v>555</v>
+      </c>
+      <c r="C105" t="s">
+        <v>84</v>
+      </c>
+      <c r="D105" t="s">
+        <v>60</v>
+      </c>
+      <c r="E105" t="s">
+        <v>556</v>
+      </c>
+      <c r="F105" t="s">
+        <v>61</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>558</v>
+      </c>
+      <c r="B106" t="s">
+        <v>204</v>
+      </c>
+      <c r="C106" t="s">
+        <v>84</v>
+      </c>
+      <c r="D106" t="s">
+        <v>53</v>
+      </c>
+      <c r="E106" t="s">
+        <v>559</v>
+      </c>
+      <c r="F106" t="s">
+        <v>206</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>561</v>
+      </c>
+      <c r="B107" t="s">
+        <v>444</v>
+      </c>
+      <c r="C107" t="s">
+        <v>199</v>
+      </c>
+      <c r="D107" t="s">
+        <v>60</v>
+      </c>
+      <c r="E107" t="s">
+        <v>562</v>
+      </c>
+      <c r="F107" t="s">
+        <v>563</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>565</v>
+      </c>
+      <c r="B108" t="s">
+        <v>499</v>
+      </c>
+      <c r="C108" t="s">
+        <v>500</v>
+      </c>
+      <c r="D108" t="s">
+        <v>60</v>
+      </c>
+      <c r="E108" t="s">
+        <v>566</v>
+      </c>
+      <c r="F108" t="s">
+        <v>502</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>568</v>
+      </c>
+      <c r="B109" t="s">
+        <v>569</v>
+      </c>
+      <c r="C109" t="s">
+        <v>167</v>
+      </c>
+      <c r="D109" t="s">
+        <v>134</v>
+      </c>
+      <c r="E109" t="s">
+        <v>570</v>
+      </c>
+      <c r="F109" t="s">
+        <v>309</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>572</v>
+      </c>
+      <c r="B110" t="s">
+        <v>573</v>
+      </c>
+      <c r="C110" t="s">
+        <v>144</v>
+      </c>
+      <c r="D110" t="s">
+        <v>134</v>
+      </c>
+      <c r="E110" t="s">
+        <v>574</v>
+      </c>
+      <c r="F110" t="s">
+        <v>575</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>577</v>
+      </c>
+      <c r="B111" t="s">
+        <v>578</v>
+      </c>
+      <c r="C111" t="s">
+        <v>405</v>
+      </c>
+      <c r="D111" t="s">
+        <v>78</v>
+      </c>
+      <c r="E111" t="s">
+        <v>579</v>
+      </c>
+      <c r="F111" t="s">
+        <v>580</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>582</v>
+      </c>
+      <c r="B112" t="s">
+        <v>583</v>
+      </c>
+      <c r="C112" t="s">
+        <v>161</v>
+      </c>
+      <c r="D112" t="s">
+        <v>60</v>
+      </c>
+      <c r="E112" t="s">
+        <v>584</v>
+      </c>
+      <c r="F112" t="s">
+        <v>585</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>587</v>
+      </c>
+      <c r="B113" t="s">
+        <v>588</v>
+      </c>
+      <c r="C113" t="s">
+        <v>178</v>
+      </c>
+      <c r="D113" t="s">
+        <v>60</v>
+      </c>
+      <c r="E113" t="s">
+        <v>589</v>
+      </c>
+      <c r="F113" t="s">
+        <v>174</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>587</v>
+      </c>
+      <c r="B114" t="s">
+        <v>591</v>
+      </c>
+      <c r="C114" t="s">
+        <v>592</v>
+      </c>
+      <c r="D114" t="s">
+        <v>60</v>
+      </c>
+      <c r="E114" t="s">
+        <v>593</v>
+      </c>
+      <c r="F114" t="s">
+        <v>594</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>596</v>
+      </c>
+      <c r="B115" t="s">
+        <v>597</v>
+      </c>
+      <c r="C115" t="s">
+        <v>405</v>
+      </c>
+      <c r="D115" t="s">
+        <v>60</v>
+      </c>
+      <c r="E115" t="s">
+        <v>598</v>
+      </c>
+      <c r="F115" t="s">
+        <v>61</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>596</v>
+      </c>
+      <c r="B116" t="s">
+        <v>588</v>
+      </c>
+      <c r="C116" t="s">
+        <v>178</v>
+      </c>
+      <c r="D116" t="s">
+        <v>60</v>
+      </c>
+      <c r="E116" t="s">
+        <v>600</v>
+      </c>
+      <c r="F116" t="s">
+        <v>174</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>602</v>
+      </c>
+      <c r="B117" t="s">
+        <v>603</v>
+      </c>
+      <c r="C117" t="s">
+        <v>118</v>
+      </c>
+      <c r="D117" t="s">
+        <v>288</v>
+      </c>
+      <c r="E117" t="s">
+        <v>604</v>
+      </c>
+      <c r="F117" t="s">
+        <v>61</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>606</v>
+      </c>
+      <c r="B118" t="s">
+        <v>329</v>
+      </c>
+      <c r="C118" t="s">
+        <v>607</v>
+      </c>
+      <c r="D118" t="s">
+        <v>53</v>
+      </c>
+      <c r="E118" t="s">
+        <v>608</v>
+      </c>
+      <c r="F118" t="s">
+        <v>609</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>611</v>
+      </c>
+      <c r="B119" t="s">
+        <v>493</v>
+      </c>
+      <c r="C119" t="s">
+        <v>494</v>
+      </c>
+      <c r="D119" t="s">
+        <v>60</v>
+      </c>
+      <c r="E119" t="s">
+        <v>612</v>
+      </c>
+      <c r="F119" t="s">
+        <v>496</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>614</v>
+      </c>
+      <c r="B120" t="s">
+        <v>187</v>
+      </c>
+      <c r="C120" t="s">
+        <v>188</v>
+      </c>
+      <c r="D120" t="s">
+        <v>60</v>
+      </c>
+      <c r="E120" t="s">
+        <v>189</v>
+      </c>
+      <c r="F120" t="s">
+        <v>190</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>616</v>
+      </c>
+      <c r="B121" t="s">
+        <v>617</v>
+      </c>
+      <c r="C121" t="s">
+        <v>71</v>
+      </c>
+      <c r="D121" t="s">
+        <v>53</v>
+      </c>
+      <c r="E121" t="s">
+        <v>618</v>
+      </c>
+      <c r="F121" t="s">
+        <v>619</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>621</v>
+      </c>
+      <c r="B122" t="s">
+        <v>622</v>
+      </c>
+      <c r="C122" t="s">
+        <v>84</v>
+      </c>
+      <c r="D122" t="s">
+        <v>60</v>
+      </c>
+      <c r="E122" t="s">
+        <v>623</v>
+      </c>
+      <c r="F122" t="s">
+        <v>624</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>626</v>
+      </c>
+      <c r="B123" t="s">
+        <v>117</v>
+      </c>
+      <c r="C123" t="s">
+        <v>118</v>
+      </c>
+      <c r="D123" t="s">
+        <v>60</v>
+      </c>
+      <c r="E123" t="s">
+        <v>627</v>
+      </c>
+      <c r="F123" t="s">
+        <v>120</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>629</v>
+      </c>
+      <c r="B124" t="s">
+        <v>630</v>
+      </c>
+      <c r="C124" t="s">
+        <v>631</v>
+      </c>
+      <c r="D124" t="s">
+        <v>60</v>
+      </c>
+      <c r="E124" t="s">
+        <v>632</v>
+      </c>
+      <c r="F124" t="s">
+        <v>633</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>635</v>
+      </c>
+      <c r="B125" t="s">
+        <v>636</v>
+      </c>
+      <c r="C125" t="s">
+        <v>118</v>
+      </c>
+      <c r="D125" t="s">
+        <v>60</v>
+      </c>
+      <c r="E125" t="s">
+        <v>637</v>
+      </c>
+      <c r="F125" t="s">
+        <v>304</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>639</v>
+      </c>
+      <c r="B126" t="s">
+        <v>636</v>
+      </c>
+      <c r="C126" t="s">
+        <v>118</v>
+      </c>
+      <c r="D126" t="s">
+        <v>60</v>
+      </c>
+      <c r="E126" t="s">
+        <v>640</v>
+      </c>
+      <c r="F126" t="s">
+        <v>304</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>642</v>
+      </c>
+      <c r="B127" t="s">
+        <v>123</v>
+      </c>
+      <c r="C127" t="s">
+        <v>118</v>
+      </c>
+      <c r="D127" t="s">
+        <v>60</v>
+      </c>
+      <c r="E127" t="s">
+        <v>643</v>
+      </c>
+      <c r="F127" t="s">
         <v>128</v>
       </c>
-      <c r="D71" t="s">
-        <v>54</v>
-      </c>
-      <c r="E71" t="s">
-        <v>383</v>
-      </c>
-      <c r="F71" t="s">
-        <v>384</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>385</v>
+      <c r="H127" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>645</v>
+      </c>
+      <c r="B128" t="s">
+        <v>646</v>
+      </c>
+      <c r="C128" t="s">
+        <v>167</v>
+      </c>
+      <c r="D128" t="s">
+        <v>60</v>
+      </c>
+      <c r="E128" t="s">
+        <v>647</v>
+      </c>
+      <c r="F128" t="s">
+        <v>648</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>650</v>
+      </c>
+      <c r="B129" t="s">
+        <v>651</v>
+      </c>
+      <c r="C129" t="s">
+        <v>118</v>
+      </c>
+      <c r="D129" t="s">
+        <v>60</v>
+      </c>
+      <c r="E129" t="s">
+        <v>652</v>
+      </c>
+      <c r="F129" t="s">
+        <v>653</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>655</v>
+      </c>
+      <c r="B130" t="s">
+        <v>656</v>
+      </c>
+      <c r="C130" t="s">
+        <v>657</v>
+      </c>
+      <c r="D130" t="s">
+        <v>60</v>
+      </c>
+      <c r="E130" t="s">
+        <v>61</v>
+      </c>
+      <c r="F130" t="s">
+        <v>61</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>659</v>
+      </c>
+      <c r="B131" t="s">
+        <v>660</v>
+      </c>
+      <c r="C131" t="s">
+        <v>631</v>
+      </c>
+      <c r="D131" t="s">
+        <v>60</v>
+      </c>
+      <c r="E131" t="s">
+        <v>661</v>
+      </c>
+      <c r="F131" t="s">
+        <v>662</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>664</v>
+      </c>
+      <c r="B132" t="s">
+        <v>89</v>
+      </c>
+      <c r="C132" t="s">
+        <v>90</v>
+      </c>
+      <c r="D132" t="s">
+        <v>60</v>
+      </c>
+      <c r="E132" t="s">
+        <v>665</v>
+      </c>
+      <c r="F132" t="s">
+        <v>92</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>667</v>
+      </c>
+      <c r="B133" t="s">
+        <v>499</v>
+      </c>
+      <c r="C133" t="s">
+        <v>500</v>
+      </c>
+      <c r="D133" t="s">
+        <v>60</v>
+      </c>
+      <c r="E133" t="s">
+        <v>668</v>
+      </c>
+      <c r="F133" t="s">
+        <v>502</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>667</v>
+      </c>
+      <c r="B134" t="s">
+        <v>670</v>
+      </c>
+      <c r="C134" t="s">
+        <v>671</v>
+      </c>
+      <c r="D134" t="s">
+        <v>60</v>
+      </c>
+      <c r="E134" t="s">
+        <v>672</v>
+      </c>
+      <c r="F134" t="s">
+        <v>673</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>675</v>
+      </c>
+      <c r="B135" t="s">
+        <v>676</v>
+      </c>
+      <c r="C135" t="s">
+        <v>405</v>
+      </c>
+      <c r="D135" t="s">
+        <v>60</v>
+      </c>
+      <c r="E135" t="s">
+        <v>677</v>
+      </c>
+      <c r="F135" t="s">
+        <v>678</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>680</v>
+      </c>
+      <c r="B136" t="s">
+        <v>681</v>
+      </c>
+      <c r="C136" t="s">
+        <v>682</v>
+      </c>
+      <c r="D136" t="s">
+        <v>78</v>
+      </c>
+      <c r="E136" t="s">
+        <v>683</v>
+      </c>
+      <c r="F136" t="s">
+        <v>580</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>685</v>
+      </c>
+      <c r="B137" t="s">
+        <v>686</v>
+      </c>
+      <c r="C137" t="s">
+        <v>687</v>
+      </c>
+      <c r="D137" t="s">
+        <v>134</v>
+      </c>
+      <c r="E137" t="s">
+        <v>688</v>
+      </c>
+      <c r="F137" t="s">
+        <v>128</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>690</v>
+      </c>
+      <c r="B138" t="s">
+        <v>573</v>
+      </c>
+      <c r="C138" t="s">
+        <v>144</v>
+      </c>
+      <c r="D138" t="s">
+        <v>134</v>
+      </c>
+      <c r="E138" t="s">
+        <v>691</v>
+      </c>
+      <c r="F138" t="s">
+        <v>692</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>694</v>
+      </c>
+      <c r="B139" t="s">
+        <v>695</v>
+      </c>
+      <c r="C139" t="s">
+        <v>199</v>
+      </c>
+      <c r="D139" t="s">
+        <v>60</v>
+      </c>
+      <c r="E139" t="s">
+        <v>273</v>
+      </c>
+      <c r="F139" t="s">
+        <v>696</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>698</v>
+      </c>
+      <c r="B140" t="s">
+        <v>699</v>
+      </c>
+      <c r="C140" t="s">
+        <v>167</v>
+      </c>
+      <c r="D140" t="s">
+        <v>60</v>
+      </c>
+      <c r="E140" t="s">
+        <v>700</v>
+      </c>
+      <c r="F140" t="s">
+        <v>701</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>702</v>
       </c>
     </row>
   </sheetData>
@@ -3521,6 +6530,75 @@
     <hyperlink ref="H69" r:id="rId68"/>
     <hyperlink ref="H70" r:id="rId69"/>
     <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3529,7 +6607,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3568,8 +6646,994 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" t="s">
+        <v>705</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" t="s">
+        <v>710</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>712</v>
+      </c>
+      <c r="B4" t="s">
+        <v>713</v>
+      </c>
+      <c r="C4" t="s">
+        <v>714</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" t="s">
+        <v>715</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>717</v>
+      </c>
+      <c r="B5" t="s">
+        <v>718</v>
+      </c>
+      <c r="C5" t="s">
+        <v>719</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" t="s">
+        <v>414</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>721</v>
+      </c>
+      <c r="B6" t="s">
+        <v>722</v>
+      </c>
+      <c r="C6" t="s">
+        <v>462</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" t="s">
+        <v>723</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>725</v>
+      </c>
+      <c r="B7" t="s">
+        <v>726</v>
+      </c>
+      <c r="C7" t="s">
+        <v>727</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" t="s">
+        <v>728</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>730</v>
+      </c>
+      <c r="B8" t="s">
+        <v>731</v>
+      </c>
+      <c r="C8" t="s">
+        <v>732</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" t="s">
+        <v>710</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>734</v>
+      </c>
+      <c r="B9" t="s">
+        <v>735</v>
+      </c>
+      <c r="C9" t="s">
+        <v>736</v>
+      </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s">
+        <v>710</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>738</v>
+      </c>
+      <c r="B10" t="s">
+        <v>739</v>
+      </c>
+      <c r="C10" t="s">
+        <v>740</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
+        <v>741</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>743</v>
+      </c>
+      <c r="B11" t="s">
+        <v>744</v>
+      </c>
+      <c r="C11" t="s">
+        <v>719</v>
+      </c>
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>745</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>747</v>
+      </c>
+      <c r="B12" t="s">
+        <v>748</v>
+      </c>
+      <c r="C12" t="s">
+        <v>749</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" t="s">
+        <v>745</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>747</v>
+      </c>
+      <c r="B13" t="s">
+        <v>726</v>
+      </c>
+      <c r="C13" t="s">
+        <v>727</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" t="s">
+        <v>745</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>752</v>
+      </c>
+      <c r="B14" t="s">
+        <v>753</v>
+      </c>
+      <c r="C14" t="s">
+        <v>754</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" t="s">
+        <v>710</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>756</v>
+      </c>
+      <c r="B15" t="s">
+        <v>757</v>
+      </c>
+      <c r="C15" t="s">
+        <v>758</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" t="s">
+        <v>745</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>760</v>
+      </c>
+      <c r="B16" t="s">
+        <v>761</v>
+      </c>
+      <c r="C16" t="s">
+        <v>762</v>
+      </c>
+      <c r="D16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" t="s">
+        <v>710</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>764</v>
+      </c>
+      <c r="B17" t="s">
+        <v>765</v>
+      </c>
+      <c r="C17" t="s">
+        <v>719</v>
+      </c>
+      <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" t="s">
+        <v>705</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>767</v>
+      </c>
+      <c r="B18" t="s">
+        <v>768</v>
+      </c>
+      <c r="C18" t="s">
+        <v>769</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" t="s">
+        <v>705</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>771</v>
+      </c>
+      <c r="B19" t="s">
+        <v>772</v>
+      </c>
+      <c r="C19" t="s">
+        <v>773</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" t="s">
+        <v>705</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>775</v>
+      </c>
+      <c r="B20" t="s">
+        <v>776</v>
+      </c>
+      <c r="C20" t="s">
+        <v>719</v>
+      </c>
+      <c r="D20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" t="s">
+        <v>705</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>778</v>
+      </c>
+      <c r="B21" t="s">
+        <v>779</v>
+      </c>
+      <c r="C21" t="s">
+        <v>780</v>
+      </c>
+      <c r="D21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" t="s">
+        <v>705</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>782</v>
+      </c>
+      <c r="B22" t="s">
+        <v>783</v>
+      </c>
+      <c r="C22" t="s">
+        <v>719</v>
+      </c>
+      <c r="D22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" t="s">
+        <v>705</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>785</v>
+      </c>
+      <c r="B23" t="s">
+        <v>726</v>
+      </c>
+      <c r="C23" t="s">
+        <v>727</v>
+      </c>
+      <c r="D23" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" t="s">
+        <v>710</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>787</v>
+      </c>
+      <c r="B24" t="s">
+        <v>788</v>
+      </c>
+      <c r="C24" t="s">
+        <v>789</v>
+      </c>
+      <c r="D24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" t="s">
+        <v>710</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>791</v>
+      </c>
+      <c r="B25" t="s">
+        <v>792</v>
+      </c>
+      <c r="C25" t="s">
+        <v>793</v>
+      </c>
+      <c r="D25" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" t="s">
+        <v>710</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>795</v>
+      </c>
+      <c r="B26" t="s">
+        <v>796</v>
+      </c>
+      <c r="C26" t="s">
+        <v>797</v>
+      </c>
+      <c r="D26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" t="s">
+        <v>710</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>799</v>
+      </c>
+      <c r="B27" t="s">
+        <v>800</v>
+      </c>
+      <c r="C27" t="s">
+        <v>719</v>
+      </c>
+      <c r="D27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" t="s">
+        <v>710</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>802</v>
+      </c>
+      <c r="B28" t="s">
+        <v>704</v>
+      </c>
+      <c r="C28" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" t="s">
+        <v>710</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>804</v>
+      </c>
+      <c r="B29" t="s">
+        <v>805</v>
+      </c>
+      <c r="C29" t="s">
+        <v>806</v>
+      </c>
+      <c r="D29" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" t="s">
+        <v>710</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>808</v>
+      </c>
+      <c r="B30" t="s">
+        <v>809</v>
+      </c>
+      <c r="C30" t="s">
+        <v>719</v>
+      </c>
+      <c r="D30" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" t="s">
+        <v>810</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>812</v>
+      </c>
+      <c r="B31" t="s">
+        <v>813</v>
+      </c>
+      <c r="C31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" t="s">
+        <v>741</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>815</v>
+      </c>
+      <c r="B32" t="s">
+        <v>816</v>
+      </c>
+      <c r="C32" t="s">
+        <v>719</v>
+      </c>
+      <c r="D32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" t="s">
+        <v>728</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>815</v>
+      </c>
+      <c r="B33" t="s">
+        <v>818</v>
+      </c>
+      <c r="C33" t="s">
+        <v>819</v>
+      </c>
+      <c r="D33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" t="s">
+        <v>61</v>
+      </c>
+      <c r="F33" t="s">
+        <v>710</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>815</v>
+      </c>
+      <c r="B34" t="s">
+        <v>821</v>
+      </c>
+      <c r="C34" t="s">
+        <v>822</v>
+      </c>
+      <c r="D34" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" t="s">
+        <v>715</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>824</v>
+      </c>
+      <c r="B35" t="s">
+        <v>825</v>
+      </c>
+      <c r="C35" t="s">
+        <v>719</v>
+      </c>
+      <c r="D35" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" t="s">
+        <v>723</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>827</v>
+      </c>
+      <c r="B36" t="s">
+        <v>828</v>
+      </c>
+      <c r="C36" t="s">
+        <v>829</v>
+      </c>
+      <c r="D36" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" t="s">
+        <v>61</v>
+      </c>
+      <c r="F36" t="s">
+        <v>710</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>831</v>
+      </c>
+      <c r="B37" t="s">
+        <v>832</v>
+      </c>
+      <c r="C37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" t="s">
+        <v>741</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>834</v>
+      </c>
+      <c r="B38" t="s">
+        <v>835</v>
+      </c>
+      <c r="C38" t="s">
+        <v>836</v>
+      </c>
+      <c r="D38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" t="s">
+        <v>61</v>
+      </c>
+      <c r="F38" t="s">
+        <v>710</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>838</v>
+      </c>
+      <c r="B39" t="s">
+        <v>839</v>
+      </c>
+      <c r="C39" t="s">
+        <v>840</v>
+      </c>
+      <c r="D39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" t="s">
+        <v>810</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>842</v>
+      </c>
+      <c r="B40" t="s">
+        <v>843</v>
+      </c>
+      <c r="C40" t="s">
+        <v>758</v>
+      </c>
+      <c r="D40" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" t="s">
+        <v>705</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>845</v>
+      </c>
+      <c r="B41" t="s">
+        <v>846</v>
+      </c>
+      <c r="C41" t="s">
+        <v>719</v>
+      </c>
+      <c r="D41" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F41" t="s">
+        <v>741</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>848</v>
+      </c>
+      <c r="B42" t="s">
+        <v>849</v>
+      </c>
+      <c r="C42" t="s">
+        <v>850</v>
+      </c>
+      <c r="D42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" t="s">
+        <v>61</v>
+      </c>
+      <c r="F42" t="s">
+        <v>710</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
